--- a/实验结果.xlsx
+++ b/实验结果.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\研一\实验\MEDG_DA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D071039-8156-44B0-96C0-B1DEB110FC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA8D947-0EE2-4540-B2DA-F613B24E1E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DIRG" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="87">
   <si>
     <t>task1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -357,6 +357,30 @@
   <si>
     <t>DFD</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MLDG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERM</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MLDG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DFD</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CDDG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCFD-ML</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -576,7 +600,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -634,16 +658,58 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -655,21 +721,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -677,12 +728,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1031,7 +1076,7 @@
       </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2">
@@ -1090,7 +1135,7 @@
       </c>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="2">
         <v>51.39</v>
       </c>
@@ -1105,7 +1150,7 @@
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="2">
         <v>46.66</v>
       </c>
@@ -1203,7 +1248,7 @@
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
+      <c r="A5" s="33"/>
       <c r="B5" s="2">
         <v>42.73</v>
       </c>
@@ -1216,7 +1261,7 @@
       <c r="E5" s="2">
         <v>98.93</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="32" t="s">
         <v>0</v>
       </c>
       <c r="H5" s="2">
@@ -1234,7 +1279,7 @@
       <c r="L5" s="2">
         <v>99.62</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="32" t="s">
         <v>0</v>
       </c>
       <c r="O5" s="2"/>
@@ -1246,7 +1291,7 @@
       <c r="S5" s="2">
         <v>99.76</v>
       </c>
-      <c r="U5" s="19" t="s">
+      <c r="U5" s="32" t="s">
         <v>0</v>
       </c>
       <c r="V5" s="3"/>
@@ -1257,7 +1302,7 @@
         <v>99.62</v>
       </c>
       <c r="Y5" s="2"/>
-      <c r="AA5" s="19" t="s">
+      <c r="AA5" s="32" t="s">
         <v>0</v>
       </c>
       <c r="AB5" s="2">
@@ -1269,7 +1314,7 @@
       <c r="AD5" s="2">
         <v>99.74</v>
       </c>
-      <c r="AF5" s="19" t="s">
+      <c r="AF5" s="32" t="s">
         <v>0</v>
       </c>
       <c r="AG5" s="2">
@@ -1279,7 +1324,7 @@
         <v>99.62</v>
       </c>
       <c r="AI5" s="2"/>
-      <c r="AK5" s="19" t="s">
+      <c r="AK5" s="32" t="s">
         <v>0</v>
       </c>
       <c r="AL5" s="2"/>
@@ -1304,7 +1349,7 @@
         <f t="shared" si="0"/>
         <v>98.917500000000004</v>
       </c>
-      <c r="G6" s="20"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="2">
         <v>99.74</v>
       </c>
@@ -1320,7 +1365,7 @@
       <c r="L6" s="2">
         <v>99.66</v>
       </c>
-      <c r="N6" s="20"/>
+      <c r="N6" s="33"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
@@ -1330,7 +1375,7 @@
       <c r="S6" s="2">
         <v>99.7</v>
       </c>
-      <c r="U6" s="20"/>
+      <c r="U6" s="33"/>
       <c r="V6" s="4"/>
       <c r="W6" s="2">
         <v>99.88</v>
@@ -1339,7 +1384,7 @@
         <v>99.74</v>
       </c>
       <c r="Y6" s="2"/>
-      <c r="AA6" s="20"/>
+      <c r="AA6" s="33"/>
       <c r="AB6" s="2">
         <v>99.8</v>
       </c>
@@ -1349,7 +1394,7 @@
       <c r="AD6" s="2">
         <v>99.7</v>
       </c>
-      <c r="AF6" s="20"/>
+      <c r="AF6" s="33"/>
       <c r="AG6" s="2">
         <v>99.86</v>
       </c>
@@ -1357,13 +1402,13 @@
         <v>99.74</v>
       </c>
       <c r="AI6" s="2"/>
-      <c r="AK6" s="20"/>
+      <c r="AK6" s="33"/>
       <c r="AL6" s="2"/>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="32" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="2">
@@ -1378,7 +1423,7 @@
       <c r="E7" s="2">
         <v>95.62</v>
       </c>
-      <c r="G7" s="20"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="2">
         <v>99.86</v>
       </c>
@@ -1394,7 +1439,7 @@
       <c r="L7" s="2">
         <v>99.92</v>
       </c>
-      <c r="N7" s="20"/>
+      <c r="N7" s="33"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
@@ -1404,7 +1449,7 @@
       <c r="S7" s="2">
         <v>99.92</v>
       </c>
-      <c r="U7" s="20"/>
+      <c r="U7" s="33"/>
       <c r="V7" s="4"/>
       <c r="W7" s="2">
         <v>99.84</v>
@@ -1413,7 +1458,7 @@
         <v>99.74</v>
       </c>
       <c r="Y7" s="2"/>
-      <c r="AA7" s="20"/>
+      <c r="AA7" s="33"/>
       <c r="AB7" s="2">
         <v>99.88</v>
       </c>
@@ -1423,7 +1468,7 @@
       <c r="AD7" s="2">
         <v>99.84</v>
       </c>
-      <c r="AF7" s="20"/>
+      <c r="AF7" s="33"/>
       <c r="AG7" s="2">
         <v>99.74</v>
       </c>
@@ -1431,13 +1476,13 @@
         <v>99.74</v>
       </c>
       <c r="AI7" s="2"/>
-      <c r="AK7" s="20"/>
+      <c r="AK7" s="33"/>
       <c r="AL7" s="2"/>
       <c r="AM7" s="2"/>
       <c r="AN7" s="2"/>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="2">
         <v>51.61</v>
       </c>
@@ -1450,7 +1495,7 @@
       <c r="E8" s="2">
         <v>94.06</v>
       </c>
-      <c r="G8" s="20"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="2">
         <v>99.86</v>
       </c>
@@ -1466,7 +1511,7 @@
       <c r="L8" s="2">
         <v>99.82</v>
       </c>
-      <c r="N8" s="20"/>
+      <c r="N8" s="33"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
@@ -1476,7 +1521,7 @@
       <c r="S8" s="2">
         <v>99.72</v>
       </c>
-      <c r="U8" s="20"/>
+      <c r="U8" s="33"/>
       <c r="V8" s="4"/>
       <c r="W8" s="2">
         <v>99.6</v>
@@ -1485,7 +1530,7 @@
         <v>99.6</v>
       </c>
       <c r="Y8" s="2"/>
-      <c r="AA8" s="20"/>
+      <c r="AA8" s="33"/>
       <c r="AB8" s="2">
         <v>99.94</v>
       </c>
@@ -1495,7 +1540,7 @@
       <c r="AD8" s="2">
         <v>99.7</v>
       </c>
-      <c r="AF8" s="20"/>
+      <c r="AF8" s="33"/>
       <c r="AG8" s="2">
         <v>99.72</v>
       </c>
@@ -1503,13 +1548,13 @@
         <v>99.6</v>
       </c>
       <c r="AI8" s="2"/>
-      <c r="AK8" s="20"/>
+      <c r="AK8" s="33"/>
       <c r="AL8" s="2"/>
       <c r="AM8" s="2"/>
       <c r="AN8" s="2"/>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="2">
         <v>58.3</v>
       </c>
@@ -1610,7 +1655,7 @@
       <c r="AN9" s="5"/>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="2">
         <v>41.82</v>
       </c>
@@ -1623,7 +1668,7 @@
       <c r="E10" s="2">
         <v>92.87</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="32" t="s">
         <v>1</v>
       </c>
       <c r="H10" s="2">
@@ -1641,7 +1686,7 @@
       <c r="L10" s="2">
         <v>98.38</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" s="32" t="s">
         <v>1</v>
       </c>
       <c r="O10" s="2">
@@ -1659,7 +1704,7 @@
       <c r="S10" s="2">
         <v>98.42</v>
       </c>
-      <c r="U10" s="19" t="s">
+      <c r="U10" s="32" t="s">
         <v>1</v>
       </c>
       <c r="V10" s="3">
@@ -1674,7 +1719,7 @@
       <c r="Y10" s="2">
         <v>98.94</v>
       </c>
-      <c r="AA10" s="19" t="s">
+      <c r="AA10" s="32" t="s">
         <v>1</v>
       </c>
       <c r="AB10" s="2">
@@ -1686,7 +1731,7 @@
       <c r="AD10" s="2">
         <v>98.01</v>
       </c>
-      <c r="AF10" s="19" t="s">
+      <c r="AF10" s="32" t="s">
         <v>1</v>
       </c>
       <c r="AG10" s="2"/>
@@ -1694,7 +1739,7 @@
         <v>99.62</v>
       </c>
       <c r="AI10" s="2"/>
-      <c r="AK10" s="19" t="s">
+      <c r="AK10" s="32" t="s">
         <v>1</v>
       </c>
       <c r="AL10" s="2"/>
@@ -1719,7 +1764,7 @@
         <f>AVERAGE(E7:E10)</f>
         <v>93.3125</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="2">
         <v>99.84</v>
       </c>
@@ -1735,7 +1780,7 @@
       <c r="L11" s="2">
         <v>99.84</v>
       </c>
-      <c r="N11" s="20"/>
+      <c r="N11" s="33"/>
       <c r="O11" s="2">
         <v>99.49</v>
       </c>
@@ -1751,7 +1796,7 @@
       <c r="S11" s="2">
         <v>99.77</v>
       </c>
-      <c r="U11" s="20"/>
+      <c r="U11" s="33"/>
       <c r="V11" s="4">
         <v>99.86</v>
       </c>
@@ -1764,7 +1809,7 @@
       <c r="Y11" s="2">
         <v>99.55</v>
       </c>
-      <c r="AA11" s="20"/>
+      <c r="AA11" s="33"/>
       <c r="AB11" s="2">
         <v>99.77</v>
       </c>
@@ -1774,19 +1819,19 @@
       <c r="AD11" s="2">
         <v>99.63</v>
       </c>
-      <c r="AF11" s="20"/>
+      <c r="AF11" s="33"/>
       <c r="AG11" s="2"/>
       <c r="AH11">
         <v>99.74</v>
       </c>
       <c r="AI11" s="2"/>
-      <c r="AK11" s="20"/>
+      <c r="AK11" s="33"/>
       <c r="AL11" s="2"/>
       <c r="AM11" s="2"/>
       <c r="AN11" s="2"/>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="32" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="2"/>
@@ -1795,7 +1840,7 @@
         <v>99.78</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="G12" s="20"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="2">
         <v>97.69</v>
       </c>
@@ -1811,7 +1856,7 @@
       <c r="L12" s="2">
         <v>99.43</v>
       </c>
-      <c r="N12" s="20"/>
+      <c r="N12" s="33"/>
       <c r="O12" s="2">
         <v>97.03</v>
       </c>
@@ -1827,7 +1872,7 @@
       <c r="S12" s="2">
         <v>98.3</v>
       </c>
-      <c r="U12" s="20"/>
+      <c r="U12" s="33"/>
       <c r="V12" s="4">
         <v>98.77</v>
       </c>
@@ -1840,7 +1885,7 @@
       <c r="Y12" s="2">
         <v>98.57</v>
       </c>
-      <c r="AA12" s="20"/>
+      <c r="AA12" s="33"/>
       <c r="AB12" s="2">
         <v>98.1</v>
       </c>
@@ -1850,26 +1895,26 @@
       <c r="AD12" s="2">
         <v>97.03</v>
       </c>
-      <c r="AF12" s="20"/>
+      <c r="AF12" s="33"/>
       <c r="AG12" s="2"/>
       <c r="AH12" s="2">
         <v>99.74</v>
       </c>
       <c r="AI12" s="2"/>
-      <c r="AK12" s="20"/>
+      <c r="AK12" s="33"/>
       <c r="AL12" s="2"/>
       <c r="AM12" s="2"/>
       <c r="AN12" s="2"/>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2">
         <v>99.9</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="G13" s="20"/>
+      <c r="G13" s="33"/>
       <c r="H13" s="2">
         <v>99.26</v>
       </c>
@@ -1885,7 +1930,7 @@
       <c r="L13" s="2">
         <v>98.77</v>
       </c>
-      <c r="N13" s="20"/>
+      <c r="N13" s="33"/>
       <c r="O13" s="2">
         <v>96.68</v>
       </c>
@@ -1901,7 +1946,7 @@
       <c r="S13" s="2">
         <v>99.3</v>
       </c>
-      <c r="U13" s="20"/>
+      <c r="U13" s="33"/>
       <c r="V13" s="4">
         <v>99.12</v>
       </c>
@@ -1914,7 +1959,7 @@
       <c r="Y13" s="2">
         <v>98.67</v>
       </c>
-      <c r="AA13" s="20"/>
+      <c r="AA13" s="33"/>
       <c r="AB13" s="2">
         <v>98.69</v>
       </c>
@@ -1924,19 +1969,19 @@
       <c r="AD13" s="2">
         <v>98.4</v>
       </c>
-      <c r="AF13" s="20"/>
+      <c r="AF13" s="33"/>
       <c r="AG13" s="2"/>
       <c r="AH13" s="2">
         <v>99.6</v>
       </c>
       <c r="AI13" s="2"/>
-      <c r="AK13" s="20"/>
+      <c r="AK13" s="33"/>
       <c r="AL13" s="2"/>
       <c r="AM13" s="2"/>
       <c r="AN13" s="2"/>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2">
@@ -2028,14 +2073,14 @@
       <c r="AN14" s="5"/>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2">
         <v>99.94</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="32" t="s">
         <v>2</v>
       </c>
       <c r="H15" s="2">
@@ -2053,7 +2098,7 @@
       <c r="L15" s="2">
         <v>99.74</v>
       </c>
-      <c r="N15" s="19" t="s">
+      <c r="N15" s="32" t="s">
         <v>2</v>
       </c>
       <c r="O15" s="2">
@@ -2071,7 +2116,7 @@
       <c r="S15" s="2">
         <v>99.92</v>
       </c>
-      <c r="U15" s="19" t="s">
+      <c r="U15" s="32" t="s">
         <v>2</v>
       </c>
       <c r="V15" s="3">
@@ -2086,7 +2131,7 @@
       <c r="Y15" s="2">
         <v>99.74</v>
       </c>
-      <c r="AA15" s="19" t="s">
+      <c r="AA15" s="32" t="s">
         <v>2</v>
       </c>
       <c r="AB15" s="2"/>
@@ -2094,7 +2139,7 @@
         <v>99.88</v>
       </c>
       <c r="AD15" s="2"/>
-      <c r="AF15" s="19" t="s">
+      <c r="AF15" s="32" t="s">
         <v>2</v>
       </c>
       <c r="AG15" s="2"/>
@@ -2102,7 +2147,7 @@
         <v>99.88</v>
       </c>
       <c r="AI15" s="2"/>
-      <c r="AK15" s="19" t="s">
+      <c r="AK15" s="32" t="s">
         <v>2</v>
       </c>
       <c r="AL15" s="2"/>
@@ -2118,7 +2163,7 @@
         <v>99.855000000000004</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="G16" s="20"/>
+      <c r="G16" s="33"/>
       <c r="H16" s="2">
         <v>99.9</v>
       </c>
@@ -2134,7 +2179,7 @@
       <c r="L16" s="2">
         <v>99.96</v>
       </c>
-      <c r="N16" s="20"/>
+      <c r="N16" s="33"/>
       <c r="O16" s="2">
         <v>99.62</v>
       </c>
@@ -2150,7 +2195,7 @@
       <c r="S16" s="2">
         <v>99.9</v>
       </c>
-      <c r="U16" s="20"/>
+      <c r="U16" s="33"/>
       <c r="V16" s="4">
         <v>99.78</v>
       </c>
@@ -2163,25 +2208,25 @@
       <c r="Y16" s="2">
         <v>99.78</v>
       </c>
-      <c r="AA16" s="20"/>
+      <c r="AA16" s="33"/>
       <c r="AB16" s="2"/>
       <c r="AC16" s="2">
         <v>100</v>
       </c>
       <c r="AD16" s="2"/>
-      <c r="AF16" s="20"/>
+      <c r="AF16" s="33"/>
       <c r="AG16" s="2"/>
       <c r="AH16" s="2">
         <v>100</v>
       </c>
       <c r="AI16" s="2"/>
-      <c r="AK16" s="20"/>
+      <c r="AK16" s="33"/>
       <c r="AL16" s="2"/>
       <c r="AM16" s="2"/>
       <c r="AN16" s="2"/>
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="32" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="2"/>
@@ -2192,7 +2237,7 @@
         <v>97.02</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="G17" s="20"/>
+      <c r="G17" s="33"/>
       <c r="H17" s="2">
         <v>99.8</v>
       </c>
@@ -2208,7 +2253,7 @@
       <c r="L17" s="2">
         <v>99.72</v>
       </c>
-      <c r="N17" s="20"/>
+      <c r="N17" s="33"/>
       <c r="O17" s="2">
         <v>99.66</v>
       </c>
@@ -2224,7 +2269,7 @@
       <c r="S17" s="2">
         <v>99.78</v>
       </c>
-      <c r="U17" s="20"/>
+      <c r="U17" s="33"/>
       <c r="V17" s="4">
         <v>99.8</v>
       </c>
@@ -2237,25 +2282,25 @@
       <c r="Y17" s="2">
         <v>99.86</v>
       </c>
-      <c r="AA17" s="20"/>
+      <c r="AA17" s="33"/>
       <c r="AB17" s="2"/>
       <c r="AC17" s="2">
         <v>99.94</v>
       </c>
       <c r="AD17" s="2"/>
-      <c r="AF17" s="20"/>
+      <c r="AF17" s="33"/>
       <c r="AG17" s="2"/>
       <c r="AH17" s="2">
         <v>99.94</v>
       </c>
       <c r="AI17" s="2"/>
-      <c r="AK17" s="20"/>
+      <c r="AK17" s="33"/>
       <c r="AL17" s="2"/>
       <c r="AM17" s="2"/>
       <c r="AN17" s="2"/>
     </row>
     <row r="18" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2">
         <v>99.34</v>
@@ -2264,7 +2309,7 @@
         <v>99.41</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="G18" s="20"/>
+      <c r="G18" s="33"/>
       <c r="H18" s="2">
         <v>99.94</v>
       </c>
@@ -2280,7 +2325,7 @@
       <c r="L18" s="2">
         <v>99.68</v>
       </c>
-      <c r="N18" s="20"/>
+      <c r="N18" s="33"/>
       <c r="O18" s="2">
         <v>99.58</v>
       </c>
@@ -2296,7 +2341,7 @@
       <c r="S18" s="2">
         <v>99.88</v>
       </c>
-      <c r="U18" s="20"/>
+      <c r="U18" s="33"/>
       <c r="V18" s="4">
         <v>99.84</v>
       </c>
@@ -2309,25 +2354,25 @@
       <c r="Y18" s="2">
         <v>99.88</v>
       </c>
-      <c r="AA18" s="20"/>
+      <c r="AA18" s="33"/>
       <c r="AB18" s="2"/>
       <c r="AC18" s="2">
         <v>99.86</v>
       </c>
       <c r="AD18" s="2"/>
-      <c r="AF18" s="20"/>
+      <c r="AF18" s="33"/>
       <c r="AG18" s="2"/>
       <c r="AH18" s="2">
         <v>99.86</v>
       </c>
       <c r="AI18" s="2"/>
-      <c r="AK18" s="20"/>
+      <c r="AK18" s="33"/>
       <c r="AL18" s="2"/>
       <c r="AM18" s="2"/>
       <c r="AN18" s="2"/>
     </row>
     <row r="19" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
+      <c r="A19" s="33"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2">
         <v>97.33</v>
@@ -2415,7 +2460,7 @@
       <c r="AN19" s="5"/>
     </row>
     <row r="20" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2">
         <v>94.91</v>
@@ -2424,7 +2469,7 @@
         <v>94.62</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="32" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="2">
@@ -2442,7 +2487,7 @@
       <c r="L20" s="2">
         <v>95.95</v>
       </c>
-      <c r="N20" s="19" t="s">
+      <c r="N20" s="32" t="s">
         <v>3</v>
       </c>
       <c r="O20" s="2">
@@ -2460,7 +2505,7 @@
       <c r="S20" s="2">
         <v>99.87</v>
       </c>
-      <c r="U20" s="19" t="s">
+      <c r="U20" s="32" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3">
@@ -2475,7 +2520,7 @@
       <c r="Y20" s="2">
         <v>96.05</v>
       </c>
-      <c r="AA20" s="19" t="s">
+      <c r="AA20" s="32" t="s">
         <v>3</v>
       </c>
       <c r="AB20" s="2">
@@ -2487,7 +2532,7 @@
       <c r="AD20" s="2">
         <v>99.69</v>
       </c>
-      <c r="AF20" s="19" t="s">
+      <c r="AF20" s="32" t="s">
         <v>3</v>
       </c>
       <c r="AG20" s="2">
@@ -2497,7 +2542,7 @@
         <v>99.24</v>
       </c>
       <c r="AI20" s="2"/>
-      <c r="AK20" s="19" t="s">
+      <c r="AK20" s="32" t="s">
         <v>3</v>
       </c>
       <c r="AL20" s="2"/>
@@ -2516,7 +2561,7 @@
         <v>97.192499999999995</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="G21" s="20"/>
+      <c r="G21" s="33"/>
       <c r="H21" s="2">
         <v>99.41</v>
       </c>
@@ -2532,7 +2577,7 @@
       <c r="L21" s="2">
         <v>95.24</v>
       </c>
-      <c r="N21" s="20"/>
+      <c r="N21" s="33"/>
       <c r="O21" s="2">
         <v>92.56</v>
       </c>
@@ -2548,7 +2593,7 @@
       <c r="S21" s="2">
         <v>96</v>
       </c>
-      <c r="U21" s="20"/>
+      <c r="U21" s="33"/>
       <c r="V21" s="4">
         <v>95.94</v>
       </c>
@@ -2561,7 +2606,7 @@
       <c r="Y21" s="2">
         <v>94.42</v>
       </c>
-      <c r="AA21" s="20"/>
+      <c r="AA21" s="33"/>
       <c r="AB21" s="2">
         <v>96.8</v>
       </c>
@@ -2571,7 +2616,7 @@
       <c r="AD21" s="2">
         <v>96.15</v>
       </c>
-      <c r="AF21" s="20"/>
+      <c r="AF21" s="33"/>
       <c r="AG21" s="2">
         <v>93.11</v>
       </c>
@@ -2579,13 +2624,13 @@
         <v>99.72</v>
       </c>
       <c r="AI21" s="2"/>
-      <c r="AK21" s="20"/>
+      <c r="AK21" s="33"/>
       <c r="AL21" s="2"/>
       <c r="AM21" s="2"/>
       <c r="AN21" s="2"/>
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="G22" s="20"/>
+      <c r="G22" s="33"/>
       <c r="H22" s="2">
         <v>97.72</v>
       </c>
@@ -2601,7 +2646,7 @@
       <c r="L22" s="2">
         <v>99.85</v>
       </c>
-      <c r="N22" s="20"/>
+      <c r="N22" s="33"/>
       <c r="O22" s="2">
         <v>96.18</v>
       </c>
@@ -2617,7 +2662,7 @@
       <c r="S22" s="2">
         <v>96.21</v>
       </c>
-      <c r="U22" s="20"/>
+      <c r="U22" s="33"/>
       <c r="V22" s="4">
         <v>97.09</v>
       </c>
@@ -2630,7 +2675,7 @@
       <c r="Y22" s="2">
         <v>99.52</v>
       </c>
-      <c r="AA22" s="20"/>
+      <c r="AA22" s="33"/>
       <c r="AB22" s="2">
         <v>96.16</v>
       </c>
@@ -2640,7 +2685,7 @@
       <c r="AD22" s="2">
         <v>96.83</v>
       </c>
-      <c r="AF22" s="20"/>
+      <c r="AF22" s="33"/>
       <c r="AG22" s="2">
         <v>98.69</v>
       </c>
@@ -2648,13 +2693,13 @@
         <v>99.54</v>
       </c>
       <c r="AI22" s="2"/>
-      <c r="AK22" s="20"/>
+      <c r="AK22" s="33"/>
       <c r="AL22" s="2"/>
       <c r="AM22" s="2"/>
       <c r="AN22" s="2"/>
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="G23" s="20"/>
+      <c r="G23" s="33"/>
       <c r="H23" s="2">
         <v>94.62</v>
       </c>
@@ -2670,7 +2715,7 @@
       <c r="L23" s="2">
         <v>94.22</v>
       </c>
-      <c r="N23" s="20"/>
+      <c r="N23" s="33"/>
       <c r="O23" s="2">
         <v>95.13</v>
       </c>
@@ -2686,7 +2731,7 @@
       <c r="S23" s="2">
         <v>99.94</v>
       </c>
-      <c r="U23" s="20"/>
+      <c r="U23" s="33"/>
       <c r="V23" s="4">
         <v>94.48</v>
       </c>
@@ -2699,7 +2744,7 @@
       <c r="Y23" s="2">
         <v>95.44</v>
       </c>
-      <c r="AA23" s="20"/>
+      <c r="AA23" s="33"/>
       <c r="AB23" s="2">
         <v>94.35</v>
       </c>
@@ -2709,7 +2754,7 @@
       <c r="AD23" s="2">
         <v>94.31</v>
       </c>
-      <c r="AF23" s="20"/>
+      <c r="AF23" s="33"/>
       <c r="AG23" s="2">
         <v>99.77</v>
       </c>
@@ -2717,7 +2762,7 @@
         <v>96.22</v>
       </c>
       <c r="AI23" s="2"/>
-      <c r="AK23" s="20"/>
+      <c r="AK23" s="33"/>
       <c r="AL23" s="2"/>
       <c r="AM23" s="2"/>
       <c r="AN23" s="2"/>
@@ -2922,7 +2967,7 @@
       </c>
     </row>
     <row r="27" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="30" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="2">
@@ -2946,7 +2991,7 @@
       <c r="H27" s="2">
         <v>99.62</v>
       </c>
-      <c r="J27" s="31" t="s">
+      <c r="J27" s="40" t="s">
         <v>20</v>
       </c>
       <c r="K27" s="2">
@@ -2961,7 +3006,7 @@
       <c r="N27" s="2">
         <v>99.24</v>
       </c>
-      <c r="Q27" s="19" t="s">
+      <c r="Q27" s="32" t="s">
         <v>3</v>
       </c>
       <c r="R27" s="2">
@@ -2976,13 +3021,13 @@
       <c r="U27" s="2">
         <v>80.994200000000006</v>
       </c>
-      <c r="W27" s="19" t="s">
+      <c r="W27" s="32" t="s">
         <v>0</v>
       </c>
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
-      <c r="AB27" s="19" t="s">
+      <c r="AB27" s="32" t="s">
         <v>0</v>
       </c>
       <c r="AC27" s="2">
@@ -2990,7 +3035,7 @@
       </c>
       <c r="AD27" s="2"/>
       <c r="AE27" s="2"/>
-      <c r="AG27" s="19" t="s">
+      <c r="AG27" s="32" t="s">
         <v>0</v>
       </c>
       <c r="AH27" s="2"/>
@@ -2999,7 +3044,7 @@
       <c r="AK27" s="2"/>
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A28" s="22"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="2">
         <v>99.8</v>
       </c>
@@ -3021,7 +3066,7 @@
       <c r="H28" s="2">
         <v>99.74</v>
       </c>
-      <c r="J28" s="32"/>
+      <c r="J28" s="41"/>
       <c r="K28">
         <v>99.74</v>
       </c>
@@ -3034,7 +3079,7 @@
       <c r="N28" s="2">
         <v>99.72</v>
       </c>
-      <c r="Q28" s="20"/>
+      <c r="Q28" s="33"/>
       <c r="R28" s="2">
         <v>76.462000000000003</v>
       </c>
@@ -3047,24 +3092,24 @@
       <c r="U28" s="2">
         <v>75.292400000000001</v>
       </c>
-      <c r="W28" s="19"/>
+      <c r="W28" s="32"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
-      <c r="AB28" s="20"/>
+      <c r="AB28" s="33"/>
       <c r="AC28" s="2">
         <v>99.118499999999997</v>
       </c>
       <c r="AD28" s="2"/>
       <c r="AE28" s="2"/>
-      <c r="AG28" s="20"/>
+      <c r="AG28" s="33"/>
       <c r="AH28" s="2"/>
       <c r="AI28" s="2"/>
       <c r="AJ28" s="2"/>
       <c r="AK28" s="2"/>
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A29" s="22"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="2">
         <v>99.96</v>
       </c>
@@ -3086,7 +3131,7 @@
       <c r="H29" s="2">
         <v>99.74</v>
       </c>
-      <c r="J29" s="32"/>
+      <c r="J29" s="41"/>
       <c r="K29" s="2">
         <v>99.74</v>
       </c>
@@ -3099,7 +3144,7 @@
       <c r="N29" s="2">
         <v>99.54</v>
       </c>
-      <c r="Q29" s="20"/>
+      <c r="Q29" s="33"/>
       <c r="R29" s="2">
         <v>79.093599999999995</v>
       </c>
@@ -3112,24 +3157,24 @@
       <c r="U29" s="2">
         <v>76.364500000000007</v>
       </c>
-      <c r="W29" s="19"/>
+      <c r="W29" s="32"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
-      <c r="AB29" s="20"/>
+      <c r="AB29" s="33"/>
       <c r="AC29" s="2">
         <v>99.608199999999997</v>
       </c>
       <c r="AD29" s="2"/>
       <c r="AE29" s="2"/>
-      <c r="AG29" s="20"/>
+      <c r="AG29" s="33"/>
       <c r="AH29" s="2"/>
       <c r="AI29" s="2"/>
       <c r="AJ29" s="2"/>
       <c r="AK29" s="2"/>
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A30" s="22"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="2">
         <v>99.94</v>
       </c>
@@ -3151,7 +3196,7 @@
       <c r="H30" s="2">
         <v>99.6</v>
       </c>
-      <c r="J30" s="33"/>
+      <c r="J30" s="42"/>
       <c r="K30" s="2">
         <v>99.6</v>
       </c>
@@ -3164,7 +3209,7 @@
       <c r="N30" s="2">
         <v>96.22</v>
       </c>
-      <c r="Q30" s="20"/>
+      <c r="Q30" s="33"/>
       <c r="R30" s="2">
         <v>75.438599999999994</v>
       </c>
@@ -3177,17 +3222,17 @@
       <c r="U30" s="2">
         <v>78.265100000000004</v>
       </c>
-      <c r="W30" s="19"/>
+      <c r="W30" s="32"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
-      <c r="AB30" s="20"/>
+      <c r="AB30" s="33"/>
       <c r="AC30" s="2">
         <v>100</v>
       </c>
       <c r="AD30" s="2"/>
       <c r="AE30" s="2"/>
-      <c r="AG30" s="20"/>
+      <c r="AG30" s="33"/>
       <c r="AH30" s="2"/>
       <c r="AI30" s="2"/>
       <c r="AJ30" s="2"/>
@@ -3275,7 +3320,7 @@
       <c r="AK31" s="5"/>
     </row>
     <row r="32" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="30" t="s">
         <v>1</v>
       </c>
       <c r="B32" s="2">
@@ -3299,7 +3344,7 @@
       <c r="H32" s="2">
         <v>99.59</v>
       </c>
-      <c r="J32" s="23" t="s">
+      <c r="J32" s="37" t="s">
         <v>21</v>
       </c>
       <c r="K32" s="2">
@@ -3314,7 +3359,7 @@
       <c r="N32" s="2">
         <v>81.968800000000002</v>
       </c>
-      <c r="Q32" s="19" t="s">
+      <c r="Q32" s="32" t="s">
         <v>1</v>
       </c>
       <c r="R32" s="2"/>
@@ -3323,13 +3368,13 @@
       </c>
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
-      <c r="W32" s="19" t="s">
+      <c r="W32" s="32" t="s">
         <v>1</v>
       </c>
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
-      <c r="AB32" s="19" t="s">
+      <c r="AB32" s="32" t="s">
         <v>1</v>
       </c>
       <c r="AC32" s="2">
@@ -3341,7 +3386,7 @@
       <c r="AE32" s="2">
         <v>80.672300000000007</v>
       </c>
-      <c r="AG32" s="19" t="s">
+      <c r="AG32" s="32" t="s">
         <v>1</v>
       </c>
       <c r="AH32" s="2">
@@ -3356,7 +3401,7 @@
       <c r="AK32" s="2"/>
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A33" s="22"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="2">
         <v>99.86</v>
       </c>
@@ -3378,7 +3423,7 @@
       <c r="H33" s="2">
         <v>99.82</v>
       </c>
-      <c r="J33" s="24"/>
+      <c r="J33" s="38"/>
       <c r="K33" s="2">
         <v>99.020600000000002</v>
       </c>
@@ -3391,18 +3436,18 @@
       <c r="N33" s="2">
         <v>78.801199999999994</v>
       </c>
-      <c r="Q33" s="20"/>
+      <c r="Q33" s="33"/>
       <c r="R33" s="2"/>
       <c r="S33" s="2">
         <v>89.635900000000007</v>
       </c>
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
-      <c r="W33" s="20"/>
+      <c r="W33" s="33"/>
       <c r="X33" s="2"/>
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
-      <c r="AB33" s="20"/>
+      <c r="AB33" s="33"/>
       <c r="AC33" s="2">
         <v>90.756299999999996</v>
       </c>
@@ -3412,7 +3457,7 @@
       <c r="AE33" s="2">
         <v>83.286600000000007</v>
       </c>
-      <c r="AG33" s="20"/>
+      <c r="AG33" s="33"/>
       <c r="AH33" s="2">
         <v>84.687200000000004</v>
       </c>
@@ -3425,7 +3470,7 @@
       <c r="AK33" s="2"/>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A34" s="22"/>
+      <c r="A34" s="31"/>
       <c r="B34" s="2">
         <v>96.09</v>
       </c>
@@ -3447,7 +3492,7 @@
       <c r="H34" s="2">
         <v>99.49</v>
       </c>
-      <c r="J34" s="24"/>
+      <c r="J34" s="38"/>
       <c r="K34" s="2">
         <v>96.474000000000004</v>
       </c>
@@ -3460,18 +3505,18 @@
       <c r="N34" s="2">
         <v>78.3626</v>
       </c>
-      <c r="Q34" s="20"/>
+      <c r="Q34" s="33"/>
       <c r="R34" s="2"/>
       <c r="S34" s="2">
         <v>98.412700000000001</v>
       </c>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
-      <c r="W34" s="20"/>
+      <c r="W34" s="33"/>
       <c r="X34" s="2"/>
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
-      <c r="AB34" s="20"/>
+      <c r="AB34" s="33"/>
       <c r="AC34" s="2">
         <v>92.250200000000007</v>
       </c>
@@ -3481,7 +3526,7 @@
       <c r="AE34" s="2">
         <v>81.699299999999994</v>
       </c>
-      <c r="AG34" s="20"/>
+      <c r="AG34" s="33"/>
       <c r="AH34" s="2">
         <v>80.018699999999995</v>
       </c>
@@ -3494,7 +3539,7 @@
       <c r="AK34" s="2"/>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A35" s="22"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="2">
         <v>94.27</v>
       </c>
@@ -3516,7 +3561,7 @@
       <c r="H35" s="2">
         <v>99.04</v>
       </c>
-      <c r="J35" s="25"/>
+      <c r="J35" s="39"/>
       <c r="K35" s="2">
         <v>99.510300000000001</v>
       </c>
@@ -3529,18 +3574,18 @@
       <c r="N35" s="2">
         <v>82.114999999999995</v>
       </c>
-      <c r="Q35" s="20"/>
+      <c r="Q35" s="33"/>
       <c r="R35" s="2"/>
       <c r="S35" s="2">
         <v>84.033600000000007</v>
       </c>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
-      <c r="W35" s="20"/>
+      <c r="W35" s="33"/>
       <c r="X35" s="2"/>
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
-      <c r="AB35" s="20"/>
+      <c r="AB35" s="33"/>
       <c r="AC35" s="2">
         <v>91.596599999999995</v>
       </c>
@@ -3550,7 +3595,7 @@
       <c r="AE35" s="2">
         <v>77.310900000000004</v>
       </c>
-      <c r="AG35" s="20"/>
+      <c r="AG35" s="33"/>
       <c r="AH35" s="2">
         <v>99.813299999999998</v>
       </c>
@@ -3647,7 +3692,7 @@
       <c r="AK36" s="5"/>
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="30" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="2">
@@ -3671,7 +3716,7 @@
       <c r="H37" s="2">
         <v>99.88</v>
       </c>
-      <c r="J37" s="23" t="s">
+      <c r="J37" s="37" t="s">
         <v>30</v>
       </c>
       <c r="K37" s="2">
@@ -3686,7 +3731,7 @@
       <c r="N37" s="2">
         <v>97.855800000000002</v>
       </c>
-      <c r="Q37" s="19" t="s">
+      <c r="Q37" s="32" t="s">
         <v>2</v>
       </c>
       <c r="R37" s="2"/>
@@ -3695,19 +3740,19 @@
       </c>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
-      <c r="W37" s="19" t="s">
+      <c r="W37" s="32" t="s">
         <v>2</v>
       </c>
       <c r="X37" s="2"/>
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
-      <c r="AB37" s="19" t="s">
+      <c r="AB37" s="32" t="s">
         <v>2</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
       <c r="AE37" s="2"/>
-      <c r="AG37" s="19" t="s">
+      <c r="AG37" s="32" t="s">
         <v>2</v>
       </c>
       <c r="AH37" s="2"/>
@@ -3716,7 +3761,7 @@
       <c r="AK37" s="2"/>
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A38" s="22"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="2">
         <v>99.92</v>
       </c>
@@ -3738,7 +3783,7 @@
       <c r="H38" s="2">
         <v>100</v>
       </c>
-      <c r="J38" s="24"/>
+      <c r="J38" s="38"/>
       <c r="K38" s="2">
         <v>99.706199999999995</v>
       </c>
@@ -3751,29 +3796,29 @@
       <c r="N38" s="2">
         <v>92.738799999999998</v>
       </c>
-      <c r="Q38" s="20"/>
+      <c r="Q38" s="33"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2">
         <v>96.561899999999994</v>
       </c>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
-      <c r="W38" s="20"/>
+      <c r="W38" s="33"/>
       <c r="X38" s="2"/>
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
-      <c r="AB38" s="20"/>
+      <c r="AB38" s="33"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="2"/>
       <c r="AE38" s="2"/>
-      <c r="AG38" s="20"/>
+      <c r="AG38" s="33"/>
       <c r="AH38" s="2"/>
       <c r="AI38" s="2"/>
       <c r="AJ38" s="2"/>
       <c r="AK38" s="2"/>
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A39" s="22"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="2">
         <v>99.9</v>
       </c>
@@ -3795,7 +3840,7 @@
       <c r="H39" s="2">
         <v>99.94</v>
       </c>
-      <c r="J39" s="24"/>
+      <c r="J39" s="38"/>
       <c r="K39" s="2">
         <v>99.118499999999997</v>
       </c>
@@ -3808,29 +3853,29 @@
       <c r="N39" s="2">
         <v>95.614000000000004</v>
       </c>
-      <c r="Q39" s="20"/>
+      <c r="Q39" s="33"/>
       <c r="R39" s="2"/>
       <c r="S39" s="2">
         <v>91.944999999999993</v>
       </c>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
-      <c r="W39" s="20"/>
+      <c r="W39" s="33"/>
       <c r="X39" s="2"/>
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
-      <c r="AB39" s="20"/>
+      <c r="AB39" s="33"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="2"/>
       <c r="AE39" s="2"/>
-      <c r="AG39" s="20"/>
+      <c r="AG39" s="33"/>
       <c r="AH39" s="2"/>
       <c r="AI39" s="2"/>
       <c r="AJ39" s="2"/>
       <c r="AK39" s="2"/>
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A40" s="22"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="2">
         <v>100</v>
       </c>
@@ -3852,7 +3897,7 @@
       <c r="H40" s="2">
         <v>99.86</v>
       </c>
-      <c r="J40" s="25"/>
+      <c r="J40" s="39"/>
       <c r="K40" s="2">
         <v>99.216499999999996</v>
       </c>
@@ -3865,22 +3910,22 @@
       <c r="N40" s="2">
         <v>99.122799999999998</v>
       </c>
-      <c r="Q40" s="20"/>
+      <c r="Q40" s="33"/>
       <c r="R40" s="2"/>
       <c r="S40" s="2">
         <v>98.428299999999993</v>
       </c>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
-      <c r="W40" s="20"/>
+      <c r="W40" s="33"/>
       <c r="X40" s="2"/>
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
-      <c r="AB40" s="20"/>
+      <c r="AB40" s="33"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="2"/>
       <c r="AE40" s="2"/>
-      <c r="AG40" s="20"/>
+      <c r="AG40" s="33"/>
       <c r="AH40" s="2"/>
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
@@ -3953,7 +3998,7 @@
       <c r="AK41" s="5"/>
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="30" t="s">
         <v>3</v>
       </c>
       <c r="B42" s="2">
@@ -3977,7 +4022,7 @@
       <c r="H42" s="2">
         <v>99.24</v>
       </c>
-      <c r="J42" s="23" t="s">
+      <c r="J42" s="37" t="s">
         <v>22</v>
       </c>
       <c r="K42" s="2">
@@ -3992,7 +4037,7 @@
       <c r="N42" s="2">
         <v>82.358699999999999</v>
       </c>
-      <c r="Q42" s="19" t="s">
+      <c r="Q42" s="32" t="s">
         <v>0</v>
       </c>
       <c r="R42" s="2"/>
@@ -4000,7 +4045,7 @@
         <v>98.139099999999999</v>
       </c>
       <c r="U42" s="2"/>
-      <c r="W42" s="19" t="s">
+      <c r="W42" s="32" t="s">
         <v>3</v>
       </c>
       <c r="X42" s="2">
@@ -4012,13 +4057,13 @@
       <c r="Z42" s="2">
         <v>89.863500000000002</v>
       </c>
-      <c r="AB42" s="19" t="s">
+      <c r="AB42" s="32" t="s">
         <v>3</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" s="2"/>
       <c r="AE42" s="2"/>
-      <c r="AG42" s="19" t="s">
+      <c r="AG42" s="32" t="s">
         <v>3</v>
       </c>
       <c r="AH42" s="2"/>
@@ -4027,7 +4072,7 @@
       <c r="AK42" s="2"/>
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A43" s="22"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="2">
         <v>99.95</v>
       </c>
@@ -4049,7 +4094,7 @@
       <c r="H43" s="2">
         <v>99.72</v>
       </c>
-      <c r="J43" s="24"/>
+      <c r="J43" s="38"/>
       <c r="K43" s="2">
         <v>99.118499999999997</v>
       </c>
@@ -4062,14 +4107,14 @@
       <c r="N43" s="2">
         <v>80.214399999999998</v>
       </c>
-      <c r="Q43" s="20"/>
+      <c r="Q43" s="33"/>
       <c r="R43" s="2"/>
       <c r="S43" s="2">
         <v>99.020600000000002</v>
       </c>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
-      <c r="W43" s="20"/>
+      <c r="W43" s="33"/>
       <c r="X43" s="2">
         <v>94.590599999999995</v>
       </c>
@@ -4079,18 +4124,18 @@
       <c r="Z43" s="2">
         <v>94.736800000000002</v>
       </c>
-      <c r="AB43" s="20"/>
+      <c r="AB43" s="33"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="2"/>
       <c r="AE43" s="2"/>
-      <c r="AG43" s="20"/>
+      <c r="AG43" s="33"/>
       <c r="AH43" s="2"/>
       <c r="AI43" s="2"/>
       <c r="AJ43" s="2"/>
       <c r="AK43" s="2"/>
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A44" s="22"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="2">
         <v>96.9</v>
       </c>
@@ -4112,7 +4157,7 @@
       <c r="H44" s="2">
         <v>99.54</v>
       </c>
-      <c r="J44" s="24"/>
+      <c r="J44" s="38"/>
       <c r="K44" s="2">
         <v>99.608199999999997</v>
       </c>
@@ -4125,14 +4170,14 @@
       <c r="N44" s="2">
         <v>81.530199999999994</v>
       </c>
-      <c r="Q44" s="20"/>
+      <c r="Q44" s="33"/>
       <c r="R44" s="2"/>
       <c r="S44" s="2">
         <v>96.474000000000004</v>
       </c>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
-      <c r="W44" s="20"/>
+      <c r="W44" s="33"/>
       <c r="X44" s="2">
         <v>99.658900000000003</v>
       </c>
@@ -4142,18 +4187,18 @@
       <c r="Z44" s="2">
         <v>95.467799999999997</v>
       </c>
-      <c r="AB44" s="20"/>
+      <c r="AB44" s="33"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="2"/>
       <c r="AE44" s="2"/>
-      <c r="AG44" s="20"/>
+      <c r="AG44" s="33"/>
       <c r="AH44" s="2"/>
       <c r="AI44" s="2"/>
       <c r="AJ44" s="2"/>
       <c r="AK44" s="2"/>
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A45" s="22"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="2">
         <v>97.17</v>
       </c>
@@ -4175,7 +4220,7 @@
       <c r="H45" s="2">
         <v>96.22</v>
       </c>
-      <c r="J45" s="25"/>
+      <c r="J45" s="39"/>
       <c r="K45" s="2">
         <v>100</v>
       </c>
@@ -4188,14 +4233,14 @@
       <c r="N45" s="2">
         <v>82.992199999999997</v>
       </c>
-      <c r="Q45" s="20"/>
+      <c r="Q45" s="33"/>
       <c r="R45" s="2"/>
       <c r="S45" s="2">
         <v>99.510300000000001</v>
       </c>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
-      <c r="W45" s="20"/>
+      <c r="W45" s="33"/>
       <c r="X45" s="2">
         <v>89.814800000000005</v>
       </c>
@@ -4205,11 +4250,11 @@
       <c r="Z45" s="2">
         <v>99.512699999999995</v>
       </c>
-      <c r="AB45" s="20"/>
+      <c r="AB45" s="33"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="2"/>
       <c r="AE45" s="2"/>
-      <c r="AG45" s="20"/>
+      <c r="AG45" s="33"/>
       <c r="AH45" s="2"/>
       <c r="AI45" s="2"/>
       <c r="AJ45" s="2"/>
@@ -4291,7 +4336,7 @@
       <c r="AK46" s="5"/>
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="J47" s="26" t="s">
+      <c r="J47" s="28" t="s">
         <v>28</v>
       </c>
       <c r="K47" s="2">
@@ -4308,7 +4353,7 @@
       </c>
     </row>
     <row r="48" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="J48" s="27"/>
+      <c r="J48" s="29"/>
       <c r="K48" s="2">
         <v>99.314400000000006</v>
       </c>
@@ -4329,7 +4374,7 @@
       <c r="C49" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="27"/>
+      <c r="J49" s="29"/>
       <c r="K49" s="2">
         <v>99.020600000000002</v>
       </c>
@@ -4355,7 +4400,7 @@
       </c>
       <c r="E50" s="13"/>
       <c r="F50" s="13"/>
-      <c r="J50" s="27"/>
+      <c r="J50" s="29"/>
       <c r="K50" s="2">
         <v>100</v>
       </c>
@@ -4371,12 +4416,12 @@
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="6"/>
-      <c r="C51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="30"/>
+      <c r="C51" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="36"/>
       <c r="G51" s="17">
         <v>99.35</v>
       </c>
@@ -4418,13 +4463,21 @@
         <f>AVERAGE(C52:F52)</f>
         <v>98.995000000000005</v>
       </c>
-      <c r="J52" s="26" t="s">
+      <c r="J52" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
+      <c r="K52" s="2">
+        <v>86.41</v>
+      </c>
+      <c r="L52" s="2">
+        <v>63.83</v>
+      </c>
+      <c r="M52" s="2">
+        <v>93.14</v>
+      </c>
+      <c r="N52" s="2">
+        <v>69.760000000000005</v>
+      </c>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B53" s="7" t="s">
@@ -4446,11 +4499,19 @@
         <f t="shared" ref="G53:G57" si="34">AVERAGE(C53:F53)</f>
         <v>70.495000000000005</v>
       </c>
-      <c r="J53" s="27"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="2">
+        <v>88.69</v>
+      </c>
+      <c r="L53" s="2">
+        <v>54.16</v>
+      </c>
+      <c r="M53" s="2">
+        <v>92.22</v>
+      </c>
+      <c r="N53" s="2">
+        <v>71.03</v>
+      </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B54" s="7" t="s">
@@ -4472,11 +4533,19 @@
         <f t="shared" si="34"/>
         <v>100</v>
       </c>
-      <c r="J54" s="27"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="2">
+        <v>87.41</v>
+      </c>
+      <c r="L54" s="2">
+        <v>56.01</v>
+      </c>
+      <c r="M54" s="2">
+        <v>92.2</v>
+      </c>
+      <c r="N54" s="2">
+        <v>76.72</v>
+      </c>
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
@@ -4498,11 +4567,19 @@
         <f t="shared" si="34"/>
         <v>82.167500000000004</v>
       </c>
-      <c r="J55" s="27"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="2">
+        <v>86.12</v>
+      </c>
+      <c r="L55" s="2">
+        <v>73.8</v>
+      </c>
+      <c r="M55" s="2">
+        <v>91.71</v>
+      </c>
+      <c r="N55" s="2">
+        <v>69.989999999999995</v>
+      </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
@@ -4525,10 +4602,22 @@
         <v>83.844999999999999</v>
       </c>
       <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
+      <c r="K56" s="5">
+        <f t="shared" ref="K56:M56" si="35">AVERAGE(K52:K55)</f>
+        <v>87.157499999999999</v>
+      </c>
+      <c r="L56" s="5">
+        <f t="shared" si="35"/>
+        <v>61.95</v>
+      </c>
+      <c r="M56" s="5">
+        <f t="shared" si="35"/>
+        <v>92.317499999999995</v>
+      </c>
+      <c r="N56" s="5">
+        <f>AVERAGE(N52:N55)</f>
+        <v>71.875</v>
+      </c>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B57" s="7" t="s">
@@ -4550,30 +4639,46 @@
         <f t="shared" si="34"/>
         <v>100</v>
       </c>
-      <c r="J57" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
+      <c r="J57" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K57" s="2">
+        <v>95.4</v>
+      </c>
+      <c r="L57" s="2">
+        <v>77.22</v>
+      </c>
+      <c r="M57" s="2">
+        <v>94.99</v>
+      </c>
+      <c r="N57" s="2">
+        <v>77.73</v>
+      </c>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B58" s="6"/>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
       <c r="G58" s="17">
         <v>99.76</v>
       </c>
-      <c r="J58" s="27"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="2">
+        <v>93.93</v>
+      </c>
+      <c r="L58" s="2">
+        <v>77.959999999999994</v>
+      </c>
+      <c r="M58" s="2">
+        <v>96.86</v>
+      </c>
+      <c r="N58" s="2">
+        <v>79.09</v>
+      </c>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="7" t="s">
@@ -4595,11 +4700,19 @@
         <f>AVERAGE(C59:F59)</f>
         <v>99.71</v>
       </c>
-      <c r="J59" s="27"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="2">
+        <v>93.24</v>
+      </c>
+      <c r="L59" s="2">
+        <v>78.209999999999994</v>
+      </c>
+      <c r="M59" s="2">
+        <v>96.66</v>
+      </c>
+      <c r="N59" s="2">
+        <v>79.33</v>
+      </c>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B60" s="7" t="s">
@@ -4618,14 +4731,22 @@
         <v>81.430000000000007</v>
       </c>
       <c r="G60" s="5">
-        <f t="shared" ref="G60:G64" si="35">AVERAGE(C60:F60)</f>
+        <f t="shared" ref="G60:G64" si="36">AVERAGE(C60:F60)</f>
         <v>81.54249999999999</v>
       </c>
-      <c r="J60" s="27"/>
-      <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="2">
+        <v>94.71</v>
+      </c>
+      <c r="L60" s="2">
+        <v>78.03</v>
+      </c>
+      <c r="M60" s="2">
+        <v>96.76</v>
+      </c>
+      <c r="N60" s="2">
+        <v>78.25</v>
+      </c>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B61" s="7" t="s">
@@ -4644,14 +4765,26 @@
         <v>99.85</v>
       </c>
       <c r="G61" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>99.85</v>
       </c>
       <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
+      <c r="K61" s="5">
+        <f>AVERAGE(K57:K60)</f>
+        <v>94.32</v>
+      </c>
+      <c r="L61" s="5">
+        <f t="shared" ref="L61:N61" si="37">AVERAGE(L57:L60)</f>
+        <v>77.85499999999999</v>
+      </c>
+      <c r="M61" s="5">
+        <f t="shared" si="37"/>
+        <v>96.317499999999995</v>
+      </c>
+      <c r="N61" s="5">
+        <f t="shared" si="37"/>
+        <v>78.599999999999994</v>
+      </c>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B62" s="7" t="s">
@@ -4670,16 +4803,24 @@
         <v>75.97</v>
       </c>
       <c r="G62" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>75.960000000000008</v>
       </c>
-      <c r="J62" s="26" t="s">
+      <c r="J62" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2"/>
+      <c r="K62" s="2">
+        <v>96.180199999999999</v>
+      </c>
+      <c r="L62" s="2">
+        <v>79.271699999999996</v>
+      </c>
+      <c r="M62" s="2">
+        <v>97.642399999999995</v>
+      </c>
+      <c r="N62" s="2">
+        <v>74.512699999999995</v>
+      </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B63" s="7" t="s">
@@ -4698,14 +4839,22 @@
         <v>76.66</v>
       </c>
       <c r="G63" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>76.827499999999986</v>
       </c>
-      <c r="J63" s="27"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="2">
+        <v>97.943200000000004</v>
+      </c>
+      <c r="L63" s="2">
+        <v>77.777799999999999</v>
+      </c>
+      <c r="M63" s="2">
+        <v>95.66</v>
+      </c>
+      <c r="N63" s="2">
+        <v>79.532200000000003</v>
+      </c>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B64" s="7" t="s">
@@ -4724,18 +4873,22 @@
         <v>99.85</v>
       </c>
       <c r="G64" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>99.875</v>
       </c>
-      <c r="J64" s="27"/>
-      <c r="K64" s="2"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="2">
+        <v>95.494600000000005</v>
+      </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
     </row>
     <row r="65" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J65" s="27"/>
-      <c r="K65" s="2"/>
+      <c r="J65" s="29"/>
+      <c r="K65" s="2">
+        <v>95.936700000000002</v>
+      </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
@@ -4749,21 +4902,34 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="J62:J65"/>
-    <mergeCell ref="J52:J55"/>
-    <mergeCell ref="C58:F58"/>
-    <mergeCell ref="C51:F51"/>
-    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="AF20:AF23"/>
+    <mergeCell ref="AK5:AK8"/>
+    <mergeCell ref="AK10:AK13"/>
+    <mergeCell ref="AK15:AK18"/>
+    <mergeCell ref="AK20:AK23"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA10:AA13"/>
+    <mergeCell ref="AA15:AA18"/>
+    <mergeCell ref="AA20:AA23"/>
+    <mergeCell ref="Q32:Q35"/>
+    <mergeCell ref="W27:W30"/>
     <mergeCell ref="Q27:Q30"/>
-    <mergeCell ref="J47:J50"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="J42:J45"/>
-    <mergeCell ref="J32:J35"/>
-    <mergeCell ref="J27:J30"/>
-    <mergeCell ref="Q37:Q40"/>
-    <mergeCell ref="Q42:Q45"/>
-    <mergeCell ref="J57:J60"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="W32:W35"/>
+    <mergeCell ref="W37:W40"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G15:G18"/>
+    <mergeCell ref="G20:G23"/>
+    <mergeCell ref="N5:N8"/>
+    <mergeCell ref="N10:N13"/>
+    <mergeCell ref="N15:N18"/>
+    <mergeCell ref="N20:N23"/>
+    <mergeCell ref="J37:J40"/>
     <mergeCell ref="AG27:AG30"/>
     <mergeCell ref="AG32:AG35"/>
     <mergeCell ref="AG37:AG40"/>
@@ -4780,33 +4946,20 @@
     <mergeCell ref="AF5:AF8"/>
     <mergeCell ref="AF10:AF13"/>
     <mergeCell ref="AF15:AF18"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="W32:W35"/>
-    <mergeCell ref="W37:W40"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G15:G18"/>
-    <mergeCell ref="G20:G23"/>
-    <mergeCell ref="N5:N8"/>
-    <mergeCell ref="N10:N13"/>
-    <mergeCell ref="N15:N18"/>
-    <mergeCell ref="N20:N23"/>
-    <mergeCell ref="J37:J40"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA10:AA13"/>
-    <mergeCell ref="AA15:AA18"/>
-    <mergeCell ref="AA20:AA23"/>
-    <mergeCell ref="Q32:Q35"/>
-    <mergeCell ref="W27:W30"/>
-    <mergeCell ref="AF20:AF23"/>
-    <mergeCell ref="AK5:AK8"/>
-    <mergeCell ref="AK10:AK13"/>
-    <mergeCell ref="AK15:AK18"/>
-    <mergeCell ref="AK20:AK23"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="J57:J60"/>
+    <mergeCell ref="Q37:Q40"/>
+    <mergeCell ref="Q42:Q45"/>
+    <mergeCell ref="J62:J65"/>
+    <mergeCell ref="J52:J55"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="J47:J50"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="J42:J45"/>
+    <mergeCell ref="J32:J35"/>
+    <mergeCell ref="J27:J30"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4819,7 +4972,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z57"/>
+  <dimension ref="A1:AB57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.77734375" customWidth="1"/>
@@ -4845,16 +4998,16 @@
       </c>
       <c r="E1" s="13"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="21" t="s">
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
       <c r="N1" s="7" t="s">
         <v>61</v>
       </c>
@@ -4890,16 +5043,16 @@
       <c r="F2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19" t="s">
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
       <c r="N2" s="2">
         <v>0.5</v>
       </c>
@@ -4935,16 +5088,16 @@
       <c r="F3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="19" t="s">
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -4962,16 +5115,16 @@
       <c r="F4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="19" t="s">
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
@@ -4989,16 +5142,16 @@
       <c r="F5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="19" t="s">
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
@@ -5032,37 +5185,37 @@
         <v>58</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="21" t="s">
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="21" t="s">
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
       <c r="U8" s="2"/>
-      <c r="V8" s="21" t="s">
+      <c r="V8" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="22"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
       <c r="Z8" s="2">
         <v>98.92</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C9">
@@ -5126,11 +5279,11 @@
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B10" s="35"/>
+      <c r="B10" s="27"/>
       <c r="C10">
         <v>100</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="28" t="s">
         <v>54</v>
       </c>
       <c r="H10" s="2">
@@ -5190,11 +5343,11 @@
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B11" s="35"/>
+      <c r="B11" s="27"/>
       <c r="C11">
         <v>100</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="29"/>
       <c r="H11" s="2">
         <v>99.870099999999994</v>
       </c>
@@ -5252,11 +5405,11 @@
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B12" s="35"/>
+      <c r="B12" s="27"/>
       <c r="C12">
         <v>100</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="2">
         <v>100</v>
       </c>
@@ -5318,7 +5471,7 @@
         <f>AVERAGE(C9:C12)</f>
         <v>100</v>
       </c>
-      <c r="G13" s="27"/>
+      <c r="G13" s="29"/>
       <c r="H13" s="2">
         <v>100</v>
       </c>
@@ -5376,7 +5529,7 @@
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C14">
@@ -5452,11 +5605,11 @@
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B15" s="35"/>
+      <c r="B15" s="27"/>
       <c r="C15">
         <v>100</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="28" t="s">
         <v>55</v>
       </c>
       <c r="H15" s="2">
@@ -5496,22 +5649,22 @@
         <v>0.98529999999999995</v>
       </c>
       <c r="U15" s="2"/>
-      <c r="V15" s="21" t="s">
+      <c r="V15" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="31"/>
       <c r="Z15" s="2">
         <v>99.87</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B16" s="35"/>
+      <c r="B16" s="27"/>
       <c r="C16">
         <v>99.685000000000002</v>
       </c>
-      <c r="G16" s="27"/>
+      <c r="G16" s="29"/>
       <c r="H16" s="2">
         <v>98.181799999999996</v>
       </c>
@@ -5569,11 +5722,11 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B17" s="35"/>
+      <c r="B17" s="27"/>
       <c r="C17">
         <v>100</v>
       </c>
-      <c r="G17" s="27"/>
+      <c r="G17" s="29"/>
       <c r="H17" s="2">
         <v>98.376599999999996</v>
       </c>
@@ -5635,7 +5788,7 @@
         <f>AVERAGE(C14:C17)</f>
         <v>99.901575000000008</v>
       </c>
-      <c r="G18" s="27"/>
+      <c r="G18" s="29"/>
       <c r="H18" s="2">
         <v>99.675299999999993</v>
       </c>
@@ -5693,7 +5846,7 @@
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C19">
@@ -5775,7 +5928,7 @@
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B20" s="35"/>
+      <c r="B20" s="27"/>
       <c r="C20">
         <v>91.3001</v>
       </c>
@@ -5785,7 +5938,7 @@
       <c r="E20">
         <v>98.924700000000001</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="28" t="s">
         <v>56</v>
       </c>
       <c r="H20" s="2">
@@ -5845,7 +5998,7 @@
       </c>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B21" s="35"/>
+      <c r="B21" s="27"/>
       <c r="C21">
         <v>96.187700000000007</v>
       </c>
@@ -5855,7 +6008,7 @@
       <c r="E21">
         <v>95.845600000000005</v>
       </c>
-      <c r="G21" s="27"/>
+      <c r="G21" s="29"/>
       <c r="H21" s="2">
         <v>99.935100000000006</v>
       </c>
@@ -5913,7 +6066,7 @@
       </c>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B22" s="35"/>
+      <c r="B22" s="27"/>
       <c r="C22">
         <v>93.939499999999995</v>
       </c>
@@ -5923,7 +6076,7 @@
       <c r="E22">
         <v>99.413499999999999</v>
       </c>
-      <c r="G22" s="27"/>
+      <c r="G22" s="29"/>
       <c r="H22" s="2">
         <v>99.935100000000006</v>
       </c>
@@ -5974,7 +6127,7 @@
         <f>AVERAGE(E19:E22)</f>
         <v>97.470675</v>
       </c>
-      <c r="G23" s="27"/>
+      <c r="G23" s="29"/>
       <c r="H23" s="2">
         <v>99.870099999999994</v>
       </c>
@@ -6013,7 +6166,7 @@
       </c>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C24">
@@ -6070,11 +6223,11 @@
       </c>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B25" s="35"/>
+      <c r="B25" s="27"/>
       <c r="C25">
         <v>99.950999999999993</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G25" s="28" t="s">
         <v>67</v>
       </c>
       <c r="H25" s="2">
@@ -6115,11 +6268,11 @@
       </c>
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B26" s="35"/>
+      <c r="B26" s="27"/>
       <c r="C26">
         <v>100</v>
       </c>
-      <c r="G26" s="27"/>
+      <c r="G26" s="29"/>
       <c r="H26" s="2">
         <v>98.960999999999999</v>
       </c>
@@ -6158,11 +6311,11 @@
       </c>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B27" s="35"/>
+      <c r="B27" s="27"/>
       <c r="C27">
         <v>99.852900000000005</v>
       </c>
-      <c r="G27" s="27"/>
+      <c r="G27" s="29"/>
       <c r="H27" s="2">
         <v>100</v>
       </c>
@@ -6201,7 +6354,7 @@
       </c>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="G28" s="27"/>
+      <c r="G28" s="29"/>
       <c r="H28" s="2">
         <v>97.207800000000006</v>
       </c>
@@ -6291,7 +6444,7 @@
       </c>
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="28" t="s">
         <v>57</v>
       </c>
       <c r="H30" s="2">
@@ -6332,7 +6485,7 @@
       </c>
     </row>
     <row r="31" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="G31" s="27"/>
+      <c r="G31" s="29"/>
       <c r="H31" s="2">
         <v>100</v>
       </c>
@@ -6371,7 +6524,7 @@
       </c>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="G32" s="27"/>
+      <c r="G32" s="29"/>
       <c r="H32" s="2">
         <v>100</v>
       </c>
@@ -6409,8 +6562,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G33" s="27"/>
+    <row r="33" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G33" s="29"/>
       <c r="H33" s="2">
         <v>99.935100000000006</v>
       </c>
@@ -6447,8 +6600,11 @@
       <c r="S33" s="2">
         <v>0.99850000000000005</v>
       </c>
-    </row>
-    <row r="34" spans="7:19" x14ac:dyDescent="0.25">
+      <c r="U33" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="7:28" x14ac:dyDescent="0.25">
       <c r="G34" s="5"/>
       <c r="H34" s="5">
         <f>AVERAGE(H30:H33)</f>
@@ -6498,554 +6654,1077 @@
         <f t="shared" si="6"/>
         <v>0.998525</v>
       </c>
-    </row>
-    <row r="36" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G36" s="18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G37" s="6"/>
-      <c r="H37" s="7" t="s">
+      <c r="U34" s="6"/>
+      <c r="V34" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="W34" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="X34" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K37" s="7" t="s">
+      <c r="Y34" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L37" s="7" t="s">
+      <c r="Z34" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="M37" s="7" t="s">
+      <c r="AA34" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="N37" s="7" t="s">
+      <c r="AB34" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G38" s="21" t="s">
+    <row r="35" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G35" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35" s="2">
+        <v>79.31</v>
+      </c>
+      <c r="I35" s="2">
+        <v>99.37</v>
+      </c>
+      <c r="J35" s="2">
+        <v>69.790000000000006</v>
+      </c>
+      <c r="K35" s="2">
+        <v>93.37</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="U35" s="30" t="s">
         <v>68</v>
       </c>
+      <c r="V35" s="2">
+        <v>100</v>
+      </c>
+      <c r="W35" s="2">
+        <v>77.9221</v>
+      </c>
+      <c r="X35" s="2">
+        <v>100</v>
+      </c>
+      <c r="Y35" s="2">
+        <v>99.94</v>
+      </c>
+      <c r="Z35" s="2">
+        <v>99.870099999999994</v>
+      </c>
+      <c r="AA35" s="2">
+        <v>100</v>
+      </c>
+      <c r="AB35" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G36" s="29"/>
+      <c r="H36" s="2">
+        <v>75.180000000000007</v>
+      </c>
+      <c r="I36" s="2">
+        <v>99.37</v>
+      </c>
+      <c r="J36" s="2">
+        <v>69.319999999999993</v>
+      </c>
+      <c r="K36" s="2">
+        <v>93.67</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="U36" s="31"/>
+      <c r="V36" s="2">
+        <v>99.935100000000006</v>
+      </c>
+      <c r="W36" s="2">
+        <v>74.805199999999999</v>
+      </c>
+      <c r="X36" s="2">
+        <v>99.94</v>
+      </c>
+      <c r="Y36" s="2">
+        <v>99.94</v>
+      </c>
+      <c r="Z36" s="2">
+        <v>100</v>
+      </c>
+      <c r="AA36" s="2">
+        <v>100</v>
+      </c>
+      <c r="AB36" s="2">
+        <v>99.870099999999994</v>
+      </c>
+    </row>
+    <row r="37" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G37" s="29"/>
+      <c r="H37" s="1">
+        <v>78.319999999999993</v>
+      </c>
+      <c r="I37" s="1">
+        <v>99.37</v>
+      </c>
+      <c r="J37" s="1">
+        <v>69.56</v>
+      </c>
+      <c r="K37" s="1">
+        <v>93.56</v>
+      </c>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="2">
+        <v>100</v>
+      </c>
+      <c r="W37" s="2">
+        <v>73.181799999999996</v>
+      </c>
+      <c r="X37" s="2">
+        <v>99.94</v>
+      </c>
+      <c r="Y37" s="2">
+        <v>99.87</v>
+      </c>
+      <c r="Z37" s="2">
+        <v>99.935100000000006</v>
+      </c>
+      <c r="AA37" s="2">
+        <v>100</v>
+      </c>
+      <c r="AB37" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G38" s="29"/>
       <c r="H38" s="2">
-        <v>100</v>
+        <v>78.13</v>
       </c>
       <c r="I38" s="2">
-        <v>77.9221</v>
+        <v>99.39</v>
       </c>
       <c r="J38" s="2">
-        <v>100</v>
+        <v>69.540000000000006</v>
       </c>
       <c r="K38" s="2">
+        <v>93.48</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="U38" s="31"/>
+      <c r="V38" s="2">
+        <v>100</v>
+      </c>
+      <c r="W38" s="2">
+        <v>78.701300000000003</v>
+      </c>
+      <c r="X38" s="2">
         <v>99.94</v>
       </c>
-      <c r="L38" s="2">
-        <v>99.870099999999994</v>
-      </c>
-      <c r="M38" s="2">
-        <v>100</v>
-      </c>
-      <c r="N38" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G39" s="22"/>
-      <c r="H39" s="2">
-        <v>99.935100000000006</v>
-      </c>
-      <c r="I39" s="2">
-        <v>74.805199999999999</v>
-      </c>
-      <c r="J39" s="2">
-        <v>99.94</v>
-      </c>
-      <c r="K39" s="2">
-        <v>99.94</v>
-      </c>
-      <c r="L39" s="2">
-        <v>100</v>
-      </c>
-      <c r="M39" s="2">
-        <v>100</v>
-      </c>
-      <c r="N39" s="2">
-        <v>99.870099999999994</v>
-      </c>
-    </row>
-    <row r="40" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G40" s="22"/>
+      <c r="Y38" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z38" s="2">
+        <v>100</v>
+      </c>
+      <c r="AA38" s="2">
+        <v>100</v>
+      </c>
+      <c r="AB38" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G39" s="25"/>
+      <c r="H39" s="5">
+        <f>AVERAGE(H35:H38)</f>
+        <v>77.734999999999999</v>
+      </c>
+      <c r="I39" s="5">
+        <f t="shared" ref="I39:K39" si="7">AVERAGE(I35:I38)</f>
+        <v>99.375</v>
+      </c>
+      <c r="J39" s="5">
+        <f t="shared" si="7"/>
+        <v>69.552500000000009</v>
+      </c>
+      <c r="K39" s="5">
+        <f t="shared" si="7"/>
+        <v>93.52000000000001</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="8">
+        <f>AVERAGE(V35:V38)</f>
+        <v>99.983775000000009</v>
+      </c>
+      <c r="W39" s="5">
+        <f t="shared" ref="W39:AA39" si="8">AVERAGE(W35:W38)</f>
+        <v>76.152600000000007</v>
+      </c>
+      <c r="X39" s="10">
+        <f t="shared" si="8"/>
+        <v>99.954999999999998</v>
+      </c>
+      <c r="Y39" s="5">
+        <f t="shared" si="8"/>
+        <v>99.9375</v>
+      </c>
+      <c r="Z39" s="10">
+        <f t="shared" si="8"/>
+        <v>99.951300000000003</v>
+      </c>
+      <c r="AA39" s="5">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+      <c r="AB39" s="5">
+        <f>AVERAGE(AB35:AB38)</f>
+        <v>99.967524999999995</v>
+      </c>
+    </row>
+    <row r="40" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G40" s="28" t="s">
+        <v>83</v>
+      </c>
       <c r="H40" s="2">
-        <v>100</v>
+        <v>81.819999999999993</v>
       </c>
       <c r="I40" s="2">
-        <v>73.181799999999996</v>
+        <v>100</v>
       </c>
       <c r="J40" s="2">
-        <v>99.94</v>
+        <v>68.959999999999994</v>
       </c>
       <c r="K40" s="2">
-        <v>99.87</v>
+        <v>94.61</v>
       </c>
       <c r="L40" s="2">
-        <v>99.935100000000006</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="M40" s="2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="N40" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G41" s="22"/>
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="O40" s="2">
+        <v>0.94740000000000002</v>
+      </c>
+      <c r="P40" s="2">
+        <v>0.8236</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>1</v>
+      </c>
+      <c r="R40" s="2">
+        <v>0.6986</v>
+      </c>
+      <c r="S40" s="2">
+        <v>0.94710000000000005</v>
+      </c>
+      <c r="U40" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="V40" s="2">
+        <v>100</v>
+      </c>
+      <c r="W40" s="2">
+        <v>98.110200000000006</v>
+      </c>
+      <c r="X40" s="2">
+        <v>100</v>
+      </c>
+      <c r="Y40" s="2">
+        <v>99.842500000000001</v>
+      </c>
+      <c r="Z40" s="2">
+        <v>99.842500000000001</v>
+      </c>
+      <c r="AA40" s="2">
+        <v>100</v>
+      </c>
+      <c r="AB40" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G41" s="29"/>
       <c r="H41" s="2">
-        <v>100</v>
+        <v>84.61</v>
       </c>
       <c r="I41" s="2">
-        <v>78.701300000000003</v>
+        <v>99.61</v>
       </c>
       <c r="J41" s="2">
-        <v>99.94</v>
+        <v>70.92</v>
       </c>
       <c r="K41" s="2">
-        <v>100</v>
+        <v>93.73</v>
       </c>
       <c r="L41" s="2">
-        <v>100</v>
+        <v>0.8488</v>
       </c>
       <c r="M41" s="2">
-        <v>100</v>
+        <v>0.99609999999999999</v>
       </c>
       <c r="N41" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G42" s="5"/>
-      <c r="H42" s="8">
-        <f>AVERAGE(H38:H41)</f>
-        <v>99.983775000000009</v>
-      </c>
-      <c r="I42" s="5">
-        <f t="shared" ref="I42:M42" si="7">AVERAGE(I38:I41)</f>
-        <v>76.152600000000007</v>
-      </c>
-      <c r="J42" s="10">
-        <f t="shared" si="7"/>
-        <v>99.954999999999998</v>
-      </c>
-      <c r="K42" s="5">
-        <f t="shared" si="7"/>
-        <v>99.9375</v>
-      </c>
-      <c r="L42" s="10">
-        <f t="shared" si="7"/>
-        <v>99.951300000000003</v>
-      </c>
-      <c r="M42" s="5">
-        <f t="shared" si="7"/>
-        <v>100</v>
-      </c>
-      <c r="N42" s="5">
-        <f>AVERAGE(N38:N41)</f>
-        <v>99.967524999999995</v>
-      </c>
-    </row>
-    <row r="43" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G43" s="21" t="s">
-        <v>69</v>
-      </c>
+        <v>0.73250000000000004</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0.9385</v>
+      </c>
+      <c r="P41" s="2">
+        <v>0.8488</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>0.99609999999999999</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0.73160000000000003</v>
+      </c>
+      <c r="S41" s="2">
+        <v>0.93859999999999999</v>
+      </c>
+      <c r="U41" s="31"/>
+      <c r="V41" s="2">
+        <v>100</v>
+      </c>
+      <c r="W41" s="2">
+        <v>99.212599999999995</v>
+      </c>
+      <c r="X41" s="2">
+        <v>99.921300000000002</v>
+      </c>
+      <c r="Y41" s="2">
+        <v>99.763800000000003</v>
+      </c>
+      <c r="Z41" s="2">
+        <v>99.606300000000005</v>
+      </c>
+      <c r="AA41" s="2">
+        <v>100</v>
+      </c>
+      <c r="AB41" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G42" s="29"/>
+      <c r="H42" s="21">
+        <v>83.23</v>
+      </c>
+      <c r="I42" s="2">
+        <v>99.89</v>
+      </c>
+      <c r="J42" s="22">
+        <v>71.319999999999993</v>
+      </c>
+      <c r="K42" s="2">
+        <v>94.45</v>
+      </c>
+      <c r="L42" s="22">
+        <v>0.83650000000000002</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2">
+        <v>0.83650000000000002</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="2">
+        <v>100</v>
+      </c>
+      <c r="W42" s="2">
+        <v>99.685000000000002</v>
+      </c>
+      <c r="X42" s="2">
+        <v>99.921300000000002</v>
+      </c>
+      <c r="Y42" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z42" s="2">
+        <v>100</v>
+      </c>
+      <c r="AA42" s="2">
+        <v>99.921300000000002</v>
+      </c>
+      <c r="AB42" s="2">
+        <v>99.842500000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G43" s="29"/>
       <c r="H43" s="2">
-        <v>100</v>
+        <v>84.55</v>
       </c>
       <c r="I43" s="2">
-        <v>98.110200000000006</v>
+        <v>100</v>
       </c>
       <c r="J43" s="2">
-        <v>100</v>
+        <v>69.89</v>
       </c>
       <c r="K43" s="2">
+        <v>95.32</v>
+      </c>
+      <c r="L43" s="2">
+        <v>0.84719999999999995</v>
+      </c>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2">
+        <v>0.84689999999999999</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="2">
+        <v>100</v>
+      </c>
+      <c r="W43" s="2">
+        <v>99.763800000000003</v>
+      </c>
+      <c r="X43" s="2">
         <v>99.842500000000001</v>
       </c>
-      <c r="L43" s="2">
+      <c r="Y43" s="2">
         <v>99.842500000000001</v>
       </c>
-      <c r="M43" s="2">
-        <v>100</v>
-      </c>
-      <c r="N43" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G44" s="22"/>
-      <c r="H44" s="2">
-        <v>100</v>
-      </c>
-      <c r="I44" s="2">
-        <v>99.212599999999995</v>
-      </c>
-      <c r="J44" s="2">
+      <c r="Z43" s="2">
+        <v>99.685000000000002</v>
+      </c>
+      <c r="AA43" s="2">
+        <v>99.842500000000001</v>
+      </c>
+      <c r="AB43" s="2">
         <v>99.921300000000002</v>
       </c>
-      <c r="K44" s="2">
-        <v>99.763800000000003</v>
-      </c>
-      <c r="L44" s="2">
-        <v>99.606300000000005</v>
-      </c>
-      <c r="M44" s="2">
-        <v>100</v>
-      </c>
-      <c r="N44" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G45" s="22"/>
+    </row>
+    <row r="44" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G44" s="25"/>
+      <c r="H44" s="5">
+        <f>AVERAGE(H40:H43)</f>
+        <v>83.552500000000009</v>
+      </c>
+      <c r="I44" s="5">
+        <f t="shared" ref="I44:S44" si="9">AVERAGE(I40:I43)</f>
+        <v>99.875</v>
+      </c>
+      <c r="J44" s="5">
+        <f t="shared" si="9"/>
+        <v>70.272499999999994</v>
+      </c>
+      <c r="K44" s="5">
+        <f t="shared" si="9"/>
+        <v>94.527500000000003</v>
+      </c>
+      <c r="L44" s="5">
+        <f t="shared" si="9"/>
+        <v>0.83912500000000001</v>
+      </c>
+      <c r="M44" s="5">
+        <f t="shared" si="9"/>
+        <v>0.99804999999999999</v>
+      </c>
+      <c r="N44" s="5">
+        <f t="shared" si="9"/>
+        <v>0.71524999999999994</v>
+      </c>
+      <c r="O44" s="5">
+        <f t="shared" si="9"/>
+        <v>0.94294999999999995</v>
+      </c>
+      <c r="P44" s="5">
+        <f t="shared" si="9"/>
+        <v>0.83895000000000008</v>
+      </c>
+      <c r="Q44" s="5">
+        <f t="shared" si="9"/>
+        <v>0.99804999999999999</v>
+      </c>
+      <c r="R44" s="5">
+        <f t="shared" si="9"/>
+        <v>0.71510000000000007</v>
+      </c>
+      <c r="S44" s="5">
+        <f t="shared" si="9"/>
+        <v>0.94284999999999997</v>
+      </c>
+      <c r="U44" s="5"/>
+      <c r="V44" s="8">
+        <f>AVERAGE(V40:V43)</f>
+        <v>100</v>
+      </c>
+      <c r="W44" s="10">
+        <f t="shared" ref="W44:AA44" si="10">AVERAGE(W40:W43)</f>
+        <v>99.192899999999995</v>
+      </c>
+      <c r="X44" s="10">
+        <f t="shared" si="10"/>
+        <v>99.921275000000009</v>
+      </c>
+      <c r="Y44" s="10">
+        <f t="shared" si="10"/>
+        <v>99.862200000000001</v>
+      </c>
+      <c r="Z44" s="10">
+        <f t="shared" si="10"/>
+        <v>99.783450000000002</v>
+      </c>
+      <c r="AA44" s="10">
+        <f t="shared" si="10"/>
+        <v>99.940949999999987</v>
+      </c>
+      <c r="AB44" s="10">
+        <f>AVERAGE(AB40:AB43)</f>
+        <v>99.940949999999987</v>
+      </c>
+    </row>
+    <row r="45" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G45" s="28" t="s">
+        <v>84</v>
+      </c>
       <c r="H45" s="2">
-        <v>100</v>
+        <v>85.909099999999995</v>
       </c>
       <c r="I45" s="2">
-        <v>99.685000000000002</v>
+        <v>99.842500000000001</v>
       </c>
       <c r="J45" s="2">
-        <v>99.921300000000002</v>
+        <v>66.226799999999997</v>
       </c>
       <c r="K45" s="2">
-        <v>100</v>
+        <v>92.058800000000005</v>
       </c>
       <c r="L45" s="2">
-        <v>100</v>
+        <v>0.86019999999999996</v>
       </c>
       <c r="M45" s="2">
-        <v>99.921300000000002</v>
+        <v>0.99839999999999995</v>
       </c>
       <c r="N45" s="2">
+        <v>0.68689999999999996</v>
+      </c>
+      <c r="O45" s="2">
+        <v>0.92120000000000002</v>
+      </c>
+      <c r="P45" s="2">
+        <v>0.85980000000000001</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>0.99839999999999995</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="S45" s="2">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="U45" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="V45" s="2">
+        <v>95.356800000000007</v>
+      </c>
+      <c r="W45" s="2">
+        <v>64.222899999999996</v>
+      </c>
+      <c r="X45" s="2">
+        <v>95.601200000000006</v>
+      </c>
+      <c r="Y45" s="2">
+        <v>95.894400000000005</v>
+      </c>
+      <c r="Z45" s="2">
+        <v>98.436000000000007</v>
+      </c>
+      <c r="AA45" s="2">
+        <v>99.413499999999999</v>
+      </c>
+      <c r="AB45" s="2">
+        <v>99.413499999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G46" s="29"/>
+      <c r="H46" s="2">
+        <v>89.545500000000004</v>
+      </c>
+      <c r="I46" s="2">
         <v>99.842500000000001</v>
       </c>
-    </row>
-    <row r="46" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G46" s="22"/>
-      <c r="H46" s="2">
-        <v>100</v>
-      </c>
-      <c r="I46" s="2">
-        <v>99.763800000000003</v>
-      </c>
       <c r="J46" s="2">
+        <v>67.253200000000007</v>
+      </c>
+      <c r="K46" s="2">
+        <v>94.607799999999997</v>
+      </c>
+      <c r="L46" s="2">
+        <v>0.89470000000000005</v>
+      </c>
+      <c r="M46" s="2">
+        <v>0.99839999999999995</v>
+      </c>
+      <c r="N46" s="2">
+        <v>0.69969999999999999</v>
+      </c>
+      <c r="O46" s="2">
+        <v>0.9476</v>
+      </c>
+      <c r="P46" s="2">
+        <v>0.89359999999999995</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>0.99839999999999995</v>
+      </c>
+      <c r="R46" s="2">
+        <v>0.69910000000000005</v>
+      </c>
+      <c r="S46" s="2">
+        <v>0.94740000000000002</v>
+      </c>
+      <c r="U46" s="31"/>
+      <c r="V46" s="2">
+        <v>93.401799999999994</v>
+      </c>
+      <c r="W46" s="2">
+        <v>66.080200000000005</v>
+      </c>
+      <c r="X46" s="2">
+        <v>99.706699999999998</v>
+      </c>
+      <c r="Y46" s="2">
+        <v>98.125399999999999</v>
+      </c>
+      <c r="Z46" s="2">
+        <v>99.511200000000002</v>
+      </c>
+      <c r="AA46" s="2">
+        <v>93.8416</v>
+      </c>
+      <c r="AB46" s="2">
+        <v>99.706699999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G47" s="29"/>
+      <c r="H47" s="21">
+        <v>84.3506</v>
+      </c>
+      <c r="I47" s="22">
+        <v>100</v>
+      </c>
+      <c r="J47" s="22">
+        <v>66.422229999999999</v>
+      </c>
+      <c r="K47" s="22">
+        <v>93.921599999999998</v>
+      </c>
+      <c r="L47" s="22">
+        <v>0.84489999999999998</v>
+      </c>
+      <c r="M47" s="22">
+        <v>1</v>
+      </c>
+      <c r="N47" s="22">
+        <v>0.68610000000000004</v>
+      </c>
+      <c r="O47" s="2">
+        <v>0.94030000000000002</v>
+      </c>
+      <c r="P47" s="2">
+        <v>0.84440000000000004</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>1</v>
+      </c>
+      <c r="R47" s="2">
+        <v>0.6845</v>
+      </c>
+      <c r="S47" s="2">
+        <v>0.94020000000000004</v>
+      </c>
+      <c r="U47" s="31"/>
+      <c r="V47" s="2">
+        <v>98.123500000000007</v>
+      </c>
+      <c r="W47" s="2">
+        <v>60.9482</v>
+      </c>
+      <c r="X47" s="2">
+        <v>92.277600000000007</v>
+      </c>
+      <c r="Y47" s="2">
+        <v>95.845600000000005</v>
+      </c>
+      <c r="Z47" s="2">
+        <v>99.902199999999993</v>
+      </c>
+      <c r="AA47" s="2">
+        <v>99.804500000000004</v>
+      </c>
+      <c r="AB47" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G48" s="29"/>
+      <c r="H48" s="2">
+        <v>86.753200000000007</v>
+      </c>
+      <c r="I48" s="2">
         <v>99.842500000000001</v>
       </c>
-      <c r="K46" s="2">
-        <v>99.842500000000001</v>
-      </c>
-      <c r="L46" s="2">
-        <v>99.685000000000002</v>
-      </c>
-      <c r="M46" s="2">
-        <v>99.842500000000001</v>
-      </c>
-      <c r="N46" s="2">
-        <v>99.921300000000002</v>
-      </c>
-    </row>
-    <row r="47" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G47" s="5"/>
-      <c r="H47" s="8">
-        <f>AVERAGE(H43:H46)</f>
-        <v>100</v>
-      </c>
-      <c r="I47" s="10">
-        <f t="shared" ref="I47:M47" si="8">AVERAGE(I43:I46)</f>
-        <v>99.192899999999995</v>
-      </c>
-      <c r="J47" s="10">
-        <f t="shared" si="8"/>
-        <v>99.921275000000009</v>
-      </c>
-      <c r="K47" s="10">
-        <f t="shared" si="8"/>
-        <v>99.862200000000001</v>
-      </c>
-      <c r="L47" s="10">
-        <f t="shared" si="8"/>
-        <v>99.783450000000002</v>
-      </c>
-      <c r="M47" s="10">
-        <f t="shared" si="8"/>
-        <v>99.940949999999987</v>
-      </c>
-      <c r="N47" s="10">
-        <f>AVERAGE(N43:N46)</f>
-        <v>99.940949999999987</v>
-      </c>
-    </row>
-    <row r="48" spans="7:19" x14ac:dyDescent="0.25">
-      <c r="G48" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="H48" s="2">
-        <v>95.356800000000007</v>
-      </c>
-      <c r="I48" s="2">
-        <v>64.222899999999996</v>
-      </c>
       <c r="J48" s="2">
-        <v>95.601200000000006</v>
+        <v>65.884699999999995</v>
       </c>
       <c r="K48" s="2">
-        <v>95.894400000000005</v>
+        <v>95.049000000000007</v>
       </c>
       <c r="L48" s="2">
-        <v>98.436000000000007</v>
+        <v>0.86650000000000005</v>
       </c>
       <c r="M48" s="2">
-        <v>99.413499999999999</v>
+        <v>0.99839999999999995</v>
       </c>
       <c r="N48" s="2">
-        <v>99.413499999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G49" s="22"/>
-      <c r="H49" s="2">
-        <v>93.401799999999994</v>
-      </c>
-      <c r="I49" s="2">
-        <v>66.080200000000005</v>
-      </c>
-      <c r="J49" s="2">
-        <v>99.706699999999998</v>
-      </c>
-      <c r="K49" s="2">
-        <v>98.125399999999999</v>
-      </c>
-      <c r="L49" s="2">
-        <v>99.511200000000002</v>
-      </c>
-      <c r="M49" s="2">
-        <v>93.8416</v>
-      </c>
-      <c r="N49" s="2">
-        <v>99.706699999999998</v>
-      </c>
-    </row>
-    <row r="50" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G50" s="22"/>
-      <c r="H50" s="2">
-        <v>98.123500000000007</v>
-      </c>
-      <c r="I50" s="2">
-        <v>60.9482</v>
-      </c>
-      <c r="J50" s="2">
-        <v>92.277600000000007</v>
-      </c>
-      <c r="K50" s="2">
-        <v>95.845600000000005</v>
-      </c>
-      <c r="L50" s="2">
-        <v>99.902199999999993</v>
-      </c>
-      <c r="M50" s="2">
+        <v>0.69179999999999997</v>
+      </c>
+      <c r="O48" s="2">
+        <v>0.95089999999999997</v>
+      </c>
+      <c r="P48" s="2">
+        <v>0.86650000000000005</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>0.99839999999999995</v>
+      </c>
+      <c r="R48" s="2">
+        <v>0.69110000000000005</v>
+      </c>
+      <c r="S48" s="2">
+        <v>0.95069999999999999</v>
+      </c>
+      <c r="U48" s="31"/>
+      <c r="V48" s="2">
         <v>99.804500000000004</v>
       </c>
-      <c r="N50" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G51" s="22"/>
-      <c r="H51" s="2">
-        <v>99.804500000000004</v>
-      </c>
-      <c r="I51" s="2">
+      <c r="W48" s="2">
         <v>66.422300000000007</v>
       </c>
-      <c r="J51" s="2">
+      <c r="X48" s="2">
         <v>95.307900000000004</v>
       </c>
-      <c r="K51" s="2">
+      <c r="Y48" s="2">
         <v>99.120199999999997</v>
       </c>
-      <c r="L51" s="2">
+      <c r="Z48" s="2">
         <v>93.646100000000004</v>
       </c>
-      <c r="M51" s="2">
+      <c r="AA48" s="2">
         <v>99.071399999999997</v>
       </c>
-      <c r="N51" s="2">
+      <c r="AB48" s="2">
         <v>99.657899999999998</v>
       </c>
     </row>
-    <row r="52" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G52" s="5"/>
-      <c r="H52" s="10">
-        <f t="shared" ref="H52:N52" si="9">AVERAGE(H48:H51)</f>
+    <row r="49" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G49" s="25"/>
+      <c r="H49" s="5">
+        <f>AVERAGE(H45:H48)</f>
+        <v>86.639600000000002</v>
+      </c>
+      <c r="I49" s="5">
+        <f t="shared" ref="I49:S49" si="11">AVERAGE(I45:I48)</f>
+        <v>99.881875000000008</v>
+      </c>
+      <c r="J49" s="5">
+        <f t="shared" si="11"/>
+        <v>66.44673250000001</v>
+      </c>
+      <c r="K49" s="5">
+        <f t="shared" si="11"/>
+        <v>93.909300000000002</v>
+      </c>
+      <c r="L49" s="5">
+        <f t="shared" si="11"/>
+        <v>0.8665750000000001</v>
+      </c>
+      <c r="M49" s="5">
+        <f t="shared" si="11"/>
+        <v>0.99879999999999991</v>
+      </c>
+      <c r="N49" s="5">
+        <f t="shared" si="11"/>
+        <v>0.69112499999999999</v>
+      </c>
+      <c r="O49" s="5">
+        <f t="shared" si="11"/>
+        <v>0.94</v>
+      </c>
+      <c r="P49" s="5">
+        <f t="shared" si="11"/>
+        <v>0.86607500000000015</v>
+      </c>
+      <c r="Q49" s="5">
+        <f t="shared" si="11"/>
+        <v>0.99879999999999991</v>
+      </c>
+      <c r="R49" s="5">
+        <f t="shared" si="11"/>
+        <v>0.69017499999999998</v>
+      </c>
+      <c r="S49" s="5">
+        <f t="shared" si="11"/>
+        <v>0.93989999999999996</v>
+      </c>
+      <c r="U49" s="5"/>
+      <c r="V49" s="10">
+        <f t="shared" ref="V49:AB49" si="12">AVERAGE(V45:V48)</f>
         <v>96.671650000000014</v>
       </c>
-      <c r="I52" s="10">
-        <f t="shared" si="9"/>
+      <c r="W49" s="10">
+        <f t="shared" si="12"/>
         <v>64.418400000000005</v>
       </c>
-      <c r="J52" s="10">
-        <f t="shared" si="9"/>
+      <c r="X49" s="10">
+        <f t="shared" si="12"/>
         <v>95.723350000000011</v>
       </c>
-      <c r="K52" s="10">
-        <f t="shared" si="9"/>
+      <c r="Y49" s="10">
+        <f t="shared" si="12"/>
         <v>97.246400000000008</v>
       </c>
-      <c r="L52" s="10">
-        <f t="shared" si="9"/>
+      <c r="Z49" s="10">
+        <f t="shared" si="12"/>
         <v>97.873874999999998</v>
       </c>
-      <c r="M52" s="10">
-        <f t="shared" si="9"/>
+      <c r="AA49" s="10">
+        <f t="shared" si="12"/>
         <v>98.032749999999993</v>
       </c>
-      <c r="N52" s="8">
-        <f t="shared" si="9"/>
+      <c r="AB49" s="8">
+        <f t="shared" si="12"/>
         <v>99.694524999999999</v>
       </c>
     </row>
-    <row r="53" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G53" s="21" t="s">
+    <row r="50" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G50" s="20"/>
+      <c r="U50" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="H53" s="2">
-        <v>100</v>
-      </c>
-      <c r="I53" s="2">
+      <c r="V50" s="2">
+        <v>100</v>
+      </c>
+      <c r="W50" s="2">
         <v>78.970600000000005</v>
       </c>
-      <c r="J53" s="2">
-        <v>100</v>
-      </c>
-      <c r="K53" s="2">
+      <c r="X50" s="2">
+        <v>100</v>
+      </c>
+      <c r="Y50" s="2">
         <v>99.950999999999993</v>
       </c>
-      <c r="L53" s="2">
-        <v>100</v>
-      </c>
-      <c r="M53" s="2">
+      <c r="Z50" s="2">
+        <v>100</v>
+      </c>
+      <c r="AA50" s="2">
         <v>99.071399999999997</v>
       </c>
-      <c r="N53" s="2">
+      <c r="AB50" s="2">
         <v>99.950999999999993</v>
       </c>
     </row>
-    <row r="54" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G54" s="22"/>
-      <c r="H54" s="2">
+    <row r="51" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G51" s="20"/>
+      <c r="U51" s="31"/>
+      <c r="V51" s="2">
         <v>99.754900000000006</v>
       </c>
-      <c r="I54" s="2">
+      <c r="W51" s="2">
         <v>86.764700000000005</v>
       </c>
-      <c r="J54" s="2">
+      <c r="X51" s="2">
         <v>99.803899999999999</v>
       </c>
-      <c r="K54" s="2">
-        <v>100</v>
-      </c>
-      <c r="L54" s="2">
-        <v>100</v>
-      </c>
-      <c r="M54" s="2">
+      <c r="Y51" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z51" s="2">
+        <v>100</v>
+      </c>
+      <c r="AA51" s="2">
         <v>99.950999999999993</v>
       </c>
-      <c r="N54" s="2">
+      <c r="AB51" s="2">
         <v>99.902000000000001</v>
       </c>
     </row>
-    <row r="55" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G55" s="22"/>
-      <c r="H55" s="2">
-        <v>100</v>
-      </c>
-      <c r="I55" s="2">
+    <row r="52" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="24"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="24"/>
+      <c r="N52" s="23"/>
+      <c r="U52" s="31"/>
+      <c r="V52" s="2">
+        <v>100</v>
+      </c>
+      <c r="W52" s="2">
         <v>83.039199999999994</v>
       </c>
-      <c r="J55" s="2">
+      <c r="X52" s="2">
         <v>99.902000000000001</v>
       </c>
-      <c r="K55" s="2">
+      <c r="Y52" s="2">
         <v>99.950999999999993</v>
       </c>
-      <c r="L55" s="2">
-        <v>100</v>
-      </c>
-      <c r="M55" s="2">
-        <v>100</v>
-      </c>
-      <c r="N55" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G56" s="22"/>
-      <c r="H56" s="2">
-        <v>100</v>
-      </c>
-      <c r="I56" s="2">
+      <c r="Z52" s="2">
+        <v>100</v>
+      </c>
+      <c r="AA52" s="2">
+        <v>100</v>
+      </c>
+      <c r="AB52" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G53" s="19"/>
+      <c r="U53" s="31"/>
+      <c r="V53" s="2">
+        <v>100</v>
+      </c>
+      <c r="W53" s="2">
         <v>87.352900000000005</v>
       </c>
-      <c r="J56" s="2">
+      <c r="X53" s="2">
         <v>99.950999999999993</v>
       </c>
-      <c r="K56" s="2">
-        <v>100</v>
-      </c>
-      <c r="L56" s="2">
+      <c r="Y53" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z53" s="2">
         <v>99.950999999999993</v>
       </c>
-      <c r="M56" s="2">
+      <c r="AA53" s="2">
         <v>99.950999999999993</v>
       </c>
-      <c r="N56" s="2">
+      <c r="AB53" s="2">
         <v>99.950999999999993</v>
       </c>
     </row>
-    <row r="57" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G57" s="5"/>
-      <c r="H57" s="10">
-        <f t="shared" ref="H57:M57" si="10">AVERAGE(H53:H56)</f>
+    <row r="54" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G54" s="20"/>
+      <c r="U54" s="5"/>
+      <c r="V54" s="10">
+        <f t="shared" ref="V54:AA54" si="13">AVERAGE(V50:V53)</f>
         <v>99.938725000000005</v>
       </c>
-      <c r="I57" s="10">
-        <f t="shared" si="10"/>
+      <c r="W54" s="10">
+        <f t="shared" si="13"/>
         <v>84.031849999999991</v>
       </c>
-      <c r="J57" s="10">
-        <f t="shared" si="10"/>
+      <c r="X54" s="10">
+        <f t="shared" si="13"/>
         <v>99.914224999999988</v>
       </c>
-      <c r="K57" s="10">
-        <f t="shared" si="10"/>
+      <c r="Y54" s="10">
+        <f t="shared" si="13"/>
         <v>99.975499999999997</v>
       </c>
-      <c r="L57" s="8">
-        <f t="shared" si="10"/>
+      <c r="Z54" s="8">
+        <f t="shared" si="13"/>
         <v>99.987750000000005</v>
       </c>
-      <c r="M57" s="10">
-        <f t="shared" si="10"/>
+      <c r="AA54" s="10">
+        <f t="shared" si="13"/>
         <v>99.743349999999992</v>
       </c>
-      <c r="N57" s="10">
-        <f>AVERAGE(N53:N56)</f>
+      <c r="AB54" s="10">
+        <f>AVERAGE(AB50:AB53)</f>
         <v>99.950999999999993</v>
       </c>
     </row>
+    <row r="55" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G55" s="20"/>
+    </row>
+    <row r="56" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="G56" s="20"/>
+    </row>
+    <row r="57" spans="7:28" x14ac:dyDescent="0.25">
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="24"/>
+      <c r="K57" s="24"/>
+      <c r="L57" s="23"/>
+      <c r="M57" s="24"/>
+      <c r="N57" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="31">
+    <mergeCell ref="V8:Y8"/>
+    <mergeCell ref="V15:Y15"/>
+    <mergeCell ref="U35:U38"/>
+    <mergeCell ref="U40:U43"/>
+    <mergeCell ref="U45:U48"/>
+    <mergeCell ref="U50:U53"/>
+    <mergeCell ref="G35:G38"/>
+    <mergeCell ref="G40:G43"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="G45:G48"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J4:L4"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="G30:G33"/>
     <mergeCell ref="H8:K8"/>
@@ -7058,34 +7737,283 @@
     <mergeCell ref="B24:B27"/>
     <mergeCell ref="G20:G23"/>
     <mergeCell ref="G25:G28"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="G38:G41"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="G43:G46"/>
-    <mergeCell ref="G48:G51"/>
-    <mergeCell ref="G53:G56"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="V8:Y8"/>
-    <mergeCell ref="V15:Y15"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2">
+        <v>87.16</v>
+      </c>
+      <c r="C2">
+        <v>61.95</v>
+      </c>
+      <c r="D2">
+        <v>91.71</v>
+      </c>
+      <c r="E2">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="F2">
+        <v>77.739999999999995</v>
+      </c>
+      <c r="G2">
+        <v>99.83</v>
+      </c>
+      <c r="H2">
+        <v>69.55</v>
+      </c>
+      <c r="I2">
+        <v>93.52</v>
+      </c>
+      <c r="J2">
+        <f>AVERAGE(B2:I2)</f>
+        <v>81.431249999999991</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3">
+        <v>98.29</v>
+      </c>
+      <c r="C3">
+        <v>88.89</v>
+      </c>
+      <c r="D3">
+        <v>95.41</v>
+      </c>
+      <c r="E3">
+        <v>80.31</v>
+      </c>
+      <c r="F3">
+        <v>98.89</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>77.28</v>
+      </c>
+      <c r="I3">
+        <v>98.3</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J9" si="0">AVERAGE(B3:I3)</f>
+        <v>92.171249999999986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4">
+        <v>99.51</v>
+      </c>
+      <c r="C4">
+        <v>97.69</v>
+      </c>
+      <c r="D4">
+        <v>98.67</v>
+      </c>
+      <c r="E4">
+        <v>96.33</v>
+      </c>
+      <c r="F4">
+        <v>99.84</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>95.14</v>
+      </c>
+      <c r="I4">
+        <v>99.46</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>98.33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5">
+        <v>99.56</v>
+      </c>
+      <c r="C5">
+        <v>87.46</v>
+      </c>
+      <c r="D5">
+        <v>95.41</v>
+      </c>
+      <c r="E5">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="F5">
+        <v>99.62</v>
+      </c>
+      <c r="G5">
+        <v>99.98</v>
+      </c>
+      <c r="H5">
+        <v>75.95</v>
+      </c>
+      <c r="I5">
+        <v>99.85</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>91.553750000000008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6">
+        <v>99.58</v>
+      </c>
+      <c r="C6">
+        <v>91.76</v>
+      </c>
+      <c r="D6">
+        <v>96.44</v>
+      </c>
+      <c r="E6">
+        <v>81.77</v>
+      </c>
+      <c r="F6">
+        <v>99.04</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>75.989999999999995</v>
+      </c>
+      <c r="I6">
+        <v>97.67</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>92.781249999999986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7">
+        <v>94.32</v>
+      </c>
+      <c r="C7">
+        <v>77.86</v>
+      </c>
+      <c r="D7">
+        <v>96.32</v>
+      </c>
+      <c r="E7">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="F7">
+        <v>83.55</v>
+      </c>
+      <c r="G7">
+        <v>99.87</v>
+      </c>
+      <c r="H7">
+        <v>70.27</v>
+      </c>
+      <c r="I7">
+        <v>94.53</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>86.914999999999992</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8">
+        <v>96.39</v>
+      </c>
+      <c r="C8">
+        <v>78.52</v>
+      </c>
+      <c r="D8">
+        <v>96.65</v>
+      </c>
+      <c r="E8">
+        <v>77.02</v>
+      </c>
+      <c r="F8">
+        <v>86.63</v>
+      </c>
+      <c r="G8">
+        <v>99.88</v>
+      </c>
+      <c r="H8">
+        <v>66.44</v>
+      </c>
+      <c r="I8">
+        <v>93.91</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>86.929999999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9">
+        <v>99.53</v>
+      </c>
+      <c r="C9">
+        <v>99.48</v>
+      </c>
+      <c r="D9">
+        <v>99.92</v>
+      </c>
+      <c r="E9">
+        <v>98.68</v>
+      </c>
+      <c r="F9">
+        <v>99.96</v>
+      </c>
+      <c r="G9">
+        <v>99.94</v>
+      </c>
+      <c r="H9">
+        <v>98.34</v>
+      </c>
+      <c r="I9">
+        <v>99.95</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>99.475000000000009</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
